--- a/file/personal/roleImportant/角色要事记录表_2026.xlsx
+++ b/file/personal/roleImportant/角色要事记录表_2026.xlsx
@@ -4,16 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22340" windowHeight="13160" tabRatio="500" activeTab="3"/>
+    <workbookView windowWidth="22340" windowHeight="13160" tabRatio="500" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="角色目录" sheetId="1" r:id="rId1"/>
     <sheet name="待办任务" sheetId="2" r:id="rId2"/>
     <sheet name="一月" sheetId="9" r:id="rId3"/>
     <sheet name="二月" sheetId="10" r:id="rId4"/>
+    <sheet name="四月" sheetId="11" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">待办任务!$A$1:$D$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">待办任务!$A$1:$D$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="83">
   <si>
     <t>角色</t>
   </si>
@@ -119,10 +120,10 @@
     <t>状态</t>
   </si>
   <si>
-    <t>调研理财途径</t>
-  </si>
-  <si>
-    <t>包括保险理财（年金/万能险等等）</t>
+    <t>理财</t>
+  </si>
+  <si>
+    <t>学习理财知识</t>
   </si>
   <si>
     <t>未进行</t>
@@ -131,12 +132,6 @@
     <t>制定理财计划</t>
   </si>
   <si>
-    <t>学习理财知识</t>
-  </si>
-  <si>
-    <t>如何抵御通货膨胀</t>
-  </si>
-  <si>
     <t>通货膨胀一直在发生，如何抵御呢？</t>
   </si>
   <si>
@@ -164,25 +159,34 @@
     <t>字体:解决不会写、写不好、写错字的问题</t>
   </si>
   <si>
-    <t>面部保养</t>
-  </si>
-  <si>
-    <t>消除脸上的斑</t>
-  </si>
-  <si>
-    <t>男性如何做好面部保养？</t>
-  </si>
-  <si>
-    <t>学习备忘整理</t>
-  </si>
-  <si>
-    <t>mac电脑中记录的学习备忘需要整理推进</t>
-  </si>
-  <si>
-    <t>工作目标</t>
-  </si>
-  <si>
-    <t>1、积累人脉,2、积累行业经验,能够为己所用,注重自身成长3、充分利用工作时间,尽量取得好成绩</t>
+    <t>重新整理归类学习资料(视频/总结)</t>
+  </si>
+  <si>
+    <t>报名并参加9/10月份的事业单位考试</t>
+  </si>
+  <si>
+    <t>关注下半年其它单位自主招生情况</t>
+  </si>
+  <si>
+    <t>身体健康</t>
+  </si>
+  <si>
+    <t>去掉脸上斑点、痘痘</t>
+  </si>
+  <si>
+    <t>整理一套适合自己的日常护理方案</t>
+  </si>
+  <si>
+    <t>做一套日常鼻炎保养方案</t>
+  </si>
+  <si>
+    <t>做一套日常心脏保养方案</t>
+  </si>
+  <si>
+    <t>工作生活</t>
+  </si>
+  <si>
+    <t>1、积累人脉,2、积累行业经验,能够为己所用,注重自身成长3、保证年终评审不能低于B</t>
   </si>
   <si>
     <t>进行中</t>
@@ -191,24 +195,47 @@
     <t>不要这么丧,工作仅仅只是工作而已</t>
   </si>
   <si>
-    <t>如何了解自己</t>
-  </si>
-  <si>
-    <t>回答为什么要了解自己?如何了解自己?自己是个怎样的人?自己想要什么?</t>
-  </si>
-  <si>
-    <t>每月反思</t>
-  </si>
-  <si>
     <t>每一个月做一次反思，看这个月有没有在能力、素养、工作、家庭、职业发展、目标实现等等各个方面有成长或进展？以及问题出在哪里？</t>
   </si>
   <si>
-    <t>全家去旅游一次</t>
-  </si>
-  <si>
     <t>去成都旅游/重庆/海南全家旅游一次</t>
   </si>
   <si>
+    <r>
+      <t>苏州</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="Helvetica Neue"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.75"/>
+        <color rgb="FF000000"/>
+        <rFont val="pingfang sc"/>
+        <charset val="134"/>
+      </rPr>
+      <t>常州社保转移到上海</t>
+    </r>
+  </si>
+  <si>
+    <t>家庭保险</t>
+  </si>
+  <si>
+    <t>员工体检</t>
+  </si>
+  <si>
+    <t>副业</t>
+  </si>
+  <si>
+    <t>实现副业盈利</t>
+  </si>
+  <si>
     <t>整体目标</t>
   </si>
   <si>
@@ -255,6 +282,27 @@
   </si>
   <si>
     <t>视频:每周5</t>
+  </si>
+  <si>
+    <t>重新整理归类学习资料(视频/总结)-电脑环境准备+技术方案</t>
+  </si>
+  <si>
+    <t>工作-完成agent的demo演示</t>
+  </si>
+  <si>
+    <t>重新整理归类学习资料(视频/总结)-开始执行</t>
+  </si>
+  <si>
+    <t>关注下半年其它单位自主招生情况-制作监控程序</t>
+  </si>
+  <si>
+    <t>去掉脸上斑点、痘痘-去医院</t>
+  </si>
+  <si>
+    <t>重新整理归类学习资料(视频/总结)-完成工作</t>
+  </si>
+  <si>
+    <t>第五周</t>
   </si>
 </sst>
 </file>
@@ -267,7 +315,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -275,9 +323,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
+      <sz val="9.75"/>
+      <color rgb="FF000000"/>
+      <name val="pingfang sc"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="SimSun"/>
       <charset val="134"/>
     </font>
@@ -443,8 +495,14 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9.75"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="45">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -477,12 +535,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.25"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFBDC0BF"/>
         <bgColor rgb="FFAAAAAA"/>
       </patternFill>
@@ -501,30 +553,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCD5B5"/>
-        <bgColor rgb="FFDCDCDC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor rgb="FF993300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFF9900"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF95B3D7"/>
         <bgColor rgb="FFAAAAAA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFF9900"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -710,7 +756,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -730,90 +776,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFA5A5A5"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFA5A5A5"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA5A5A5"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFA5A5A5"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA5A5A5"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA5A5A5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFA5A5A5"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA5A5A5"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA5A5A5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -950,21 +912,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -973,46 +932,55 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1021,10 +989,10 @@
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1033,10 +1001,10 @@
     <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1045,10 +1013,10 @@
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1057,10 +1025,10 @@
     <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1069,23 +1037,17 @@
     <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1107,16 +1069,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1125,67 +1087,91 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1583,221 +1569,221 @@
   </cols>
   <sheetData>
     <row r="1" ht="14" customHeight="1" spans="1:5">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
     </row>
     <row r="2" ht="14" customHeight="1" spans="1:5">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
     </row>
     <row r="3" ht="14" customHeight="1" spans="1:5">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
     </row>
     <row r="4" ht="14" customHeight="1" spans="1:5">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
     </row>
     <row r="5" ht="14" customHeight="1" spans="1:5">
-      <c r="A5" s="32"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
+      <c r="A5" s="40"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
     </row>
     <row r="6" ht="14" customHeight="1" spans="1:5">
-      <c r="A6" s="32"/>
-      <c r="B6" s="29"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
+      <c r="A6" s="40"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
     </row>
     <row r="7" ht="14" customHeight="1" spans="1:5">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
     </row>
     <row r="8" ht="14" customHeight="1" spans="1:5">
-      <c r="A8" s="32"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
+      <c r="A8" s="40"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
     </row>
     <row r="9" ht="14" customHeight="1" spans="1:5">
-      <c r="A9" s="32"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
+      <c r="A9" s="40"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
     </row>
     <row r="10" ht="14" customHeight="1" spans="1:5">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
     </row>
     <row r="11" ht="14" customHeight="1" spans="1:5">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
     </row>
     <row r="12" ht="14" customHeight="1" spans="1:5">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
     </row>
     <row r="13" ht="14" customHeight="1" spans="1:5">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="29"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
     </row>
     <row r="14" ht="14" customHeight="1" spans="1:5">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
     </row>
     <row r="15" ht="14" customHeight="1" spans="1:5">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
     </row>
     <row r="16" ht="14" customHeight="1" spans="1:5">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
     </row>
     <row r="17" ht="14" customHeight="1" spans="1:5">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="29"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
     </row>
     <row r="18" ht="14" customHeight="1" spans="1:5">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="29"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
     </row>
     <row r="19" ht="14" customHeight="1" spans="1:5">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
     </row>
     <row r="20" ht="14" customHeight="1" spans="1:5">
-      <c r="A20" s="32" t="s">
+      <c r="A20" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
     </row>
     <row r="21" ht="14" customHeight="1" spans="1:5">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="29"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
     </row>
     <row r="22" ht="14" customHeight="1" spans="1:5">
-      <c r="A22" s="32" t="s">
+      <c r="A22" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="29"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
     </row>
     <row r="23" ht="14" customHeight="1" spans="1:5">
-      <c r="A23" s="31" t="s">
+      <c r="A23" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
     </row>
     <row r="26" ht="13.5" customHeight="1" spans="1:5">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="41" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="27" ht="13.5" customHeight="1" spans="1:5">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="19" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="28" ht="13.5" customHeight="1" spans="1:5">
-      <c r="A28" s="24" t="s">
+      <c r="A28" s="29" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="29" ht="13.5" customHeight="1" spans="1:5">
-      <c r="A29" s="27" t="s">
+      <c r="A29" s="25" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1824,7 +1810,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultColWidth="9.64423076923077" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="16.3557692307692" style="11"/>
@@ -1849,243 +1835,340 @@
       <c r="D1" s="15" t="s">
         <v>27</v>
       </c>
+      <c r="E1" s="16"/>
     </row>
     <row r="2" ht="13.35" customHeight="1" spans="1:5">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="20" t="s">
         <v>30</v>
       </c>
+      <c r="E2" s="16"/>
     </row>
     <row r="3" ht="13.35" customHeight="1" spans="1:5">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="17"/>
+      <c r="B3" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>30</v>
       </c>
+      <c r="E3" s="16"/>
     </row>
     <row r="4" ht="13.35" customHeight="1" spans="1:5">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="20" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" ht="13.35" customHeight="1" spans="1:5">
-      <c r="A5" s="20" t="s">
+      <c r="E4" s="16"/>
+    </row>
+    <row r="5" ht="13" customHeight="1" spans="1:5">
+      <c r="A5" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>30</v>
-      </c>
+      <c r="C5" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="16"/>
     </row>
     <row r="6" ht="13" customHeight="1" spans="1:5">
-      <c r="A6" s="22" t="s">
-        <v>35</v>
-      </c>
+      <c r="A6" s="22"/>
       <c r="B6" s="6" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="D6" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="16"/>
     </row>
     <row r="7" ht="13" customHeight="1" spans="1:5">
       <c r="A7" s="22"/>
       <c r="B7" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="D7" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="16"/>
     </row>
     <row r="8" ht="13" customHeight="1" spans="1:5">
       <c r="A8" s="22"/>
       <c r="B8" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="D8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="16"/>
     </row>
     <row r="9" ht="13" customHeight="1" spans="1:5">
       <c r="A9" s="22"/>
       <c r="B9" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="D9" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="16"/>
     </row>
     <row r="10" ht="13" customHeight="1" spans="1:5">
       <c r="A10" s="22"/>
       <c r="B10" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="D10" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="16"/>
     </row>
     <row r="11" ht="13" customHeight="1" spans="1:5">
       <c r="A11" s="22"/>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="16"/>
+    </row>
+    <row r="12" ht="13" customHeight="1" spans="1:5">
+      <c r="A12" s="22"/>
+      <c r="B12" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" ht="13" customHeight="1" spans="1:5">
-      <c r="A12" s="8" t="s">
+      <c r="C12" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="16"/>
+    </row>
+    <row r="13" ht="13" customHeight="1" spans="1:5">
+      <c r="A13" s="22"/>
+      <c r="B13" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="C13" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="16"/>
+    </row>
+    <row r="14" ht="13" customHeight="1" spans="1:5">
+      <c r="A14" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="B14" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="D14" s="20" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" ht="13" customHeight="1" spans="1:5">
-      <c r="A13" s="8"/>
-      <c r="B13" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="24" t="s">
+      <c r="E14" s="16"/>
+    </row>
+    <row r="15" ht="13" customHeight="1" spans="1:5">
+      <c r="A15" s="1"/>
+      <c r="B15" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D15" s="20" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="14" ht="13" customHeight="1" spans="1:5">
-      <c r="A14" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="6" t="s">
+      <c r="E15" s="16"/>
+    </row>
+    <row r="16" ht="13" customHeight="1" spans="1:5">
+      <c r="A16" s="1"/>
+      <c r="B16" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C16" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="16"/>
+    </row>
+    <row r="17" ht="13" customHeight="1" spans="1:5">
+      <c r="A17" s="1"/>
+      <c r="B17" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="16"/>
+    </row>
+    <row r="18" ht="13" customHeight="1" spans="1:5">
+      <c r="A18" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" ht="13" customHeight="1" spans="1:5">
+      <c r="A19" s="31"/>
+      <c r="B19" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="16"/>
+    </row>
+    <row r="20" ht="13" customHeight="1" spans="1:5">
+      <c r="A20" s="31"/>
+      <c r="B20" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D20" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="16"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="32"/>
+      <c r="B21" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="20" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="15" ht="13" customHeight="1" spans="1:5">
-      <c r="A15" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" s="27" t="s">
+      <c r="E21" s="16"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="32"/>
+      <c r="B22" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" ht="13" customHeight="1" spans="1:5">
-      <c r="A16" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="26" t="s">
+      <c r="D22" s="20" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="17" ht="13" customHeight="1" spans="1:4">
-      <c r="A17" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="27" t="s">
+      <c r="E22" s="16"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="32"/>
+      <c r="B23" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D23" s="20" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="18" ht="13" customHeight="1" spans="1:4">
-      <c r="A18" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="19" t="s">
+      <c r="E23" s="16"/>
+    </row>
+    <row r="24" ht="17" spans="1:5">
+      <c r="A24" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="20" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="19" ht="13" customHeight="1"/>
+      <c r="E24" s="16"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="B25" s="35"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="B26" s="35"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="B27" s="35"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D19" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D20" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <mergeCells count="2">
-    <mergeCell ref="A6:A11"/>
-    <mergeCell ref="A12:A13"/>
+  <mergeCells count="4">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D11 D12 D13 D16 D17 D18 D19 D20 D2:D3 D4:D10 D14:D15 D21:D24">
       <formula1>"未进行,进行中,已暂停,已完成"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2110,10 +2193,10 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -2132,44 +2215,44 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>37</v>
+        <v>66</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D5" s="8"/>
     </row>
     <row r="6" ht="17" spans="1:4">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>37</v>
+        <v>67</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D6" s="8"/>
     </row>
     <row r="7" ht="17" spans="1:4">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="8"/>
@@ -2177,19 +2260,19 @@
     <row r="8" ht="17" spans="1:4">
       <c r="A8" s="5"/>
       <c r="B8" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>37</v>
+        <v>69</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D8" s="8"/>
     </row>
     <row r="9" ht="17" spans="1:4">
       <c r="A9" s="5"/>
       <c r="B9" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>30</v>
       </c>
       <c r="D9" s="8"/>
@@ -2197,41 +2280,41 @@
     <row r="10" ht="17" spans="1:4">
       <c r="A10" s="5"/>
       <c r="B10" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="8"/>
     </row>
     <row r="11" ht="17" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>37</v>
+        <v>66</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D11" s="8"/>
     </row>
     <row r="12" ht="17" spans="1:4">
       <c r="A12" s="5"/>
       <c r="B12" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>37</v>
+        <v>67</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D12" s="8"/>
     </row>
     <row r="13" ht="17" spans="1:4">
       <c r="A13" s="5"/>
       <c r="B13" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>30</v>
       </c>
       <c r="D13" s="8"/>
@@ -2239,61 +2322,61 @@
     <row r="14" ht="17" spans="1:4">
       <c r="A14" s="5"/>
       <c r="B14" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>37</v>
+        <v>69</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D14" s="8"/>
     </row>
     <row r="15" ht="17" spans="1:4">
       <c r="A15" s="5"/>
       <c r="B15" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>37</v>
+        <v>70</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D15" s="8"/>
     </row>
     <row r="16" ht="17" spans="1:4">
       <c r="A16" s="5"/>
       <c r="B16" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>37</v>
+        <v>71</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D16" s="8"/>
     </row>
     <row r="17" ht="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>37</v>
+        <v>66</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D17" s="8"/>
     </row>
     <row r="18" ht="17" spans="1:4">
       <c r="A18" s="5"/>
       <c r="B18" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>37</v>
+        <v>67</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D18" s="8"/>
     </row>
     <row r="19" ht="17" spans="1:4">
       <c r="A19" s="5"/>
       <c r="B19" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>30</v>
       </c>
       <c r="D19" s="8"/>
@@ -2301,92 +2384,92 @@
     <row r="20" ht="17" spans="1:4">
       <c r="A20" s="5"/>
       <c r="B20" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>37</v>
+        <v>69</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D20" s="8"/>
     </row>
     <row r="21" ht="17" spans="1:4">
       <c r="A21" s="5"/>
       <c r="B21" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>37</v>
+        <v>70</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D21" s="8"/>
     </row>
     <row r="22" ht="17" spans="1:4">
       <c r="A22" s="5"/>
       <c r="B22" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>37</v>
+        <v>71</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D22" s="8"/>
     </row>
     <row r="23" ht="17" spans="1:4">
       <c r="A23" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>37</v>
+        <v>66</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D23" s="8"/>
     </row>
     <row r="24" ht="17" spans="1:4">
       <c r="A24" s="5"/>
       <c r="B24" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>37</v>
+        <v>67</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D24" s="8"/>
     </row>
     <row r="25" ht="17" spans="1:4">
       <c r="A25" s="5"/>
       <c r="B25" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>37</v>
+        <v>68</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D25" s="8"/>
     </row>
     <row r="26" ht="17" spans="1:4">
       <c r="A26" s="5"/>
       <c r="B26" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>37</v>
+        <v>69</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D26" s="8"/>
     </row>
     <row r="27" ht="17" spans="1:4">
       <c r="A27" s="5"/>
       <c r="B27" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>37</v>
+        <v>70</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D27" s="8"/>
     </row>
     <row r="28" ht="17" spans="1:4">
       <c r="A28" s="5"/>
       <c r="B28" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>37</v>
+        <v>71</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D28" s="8"/>
     </row>
@@ -2402,7 +2485,7 @@
     <mergeCell ref="A23:A28"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23 C24 C25 C26 C27 C28 C5:C22">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C28">
       <formula1>"未进行,进行中,已暂停,已完成"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2424,10 +2507,10 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -2446,86 +2529,86 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>37</v>
+        <v>66</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D5" s="8"/>
     </row>
     <row r="6" ht="17" spans="1:4">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>37</v>
+        <v>67</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D6" s="8"/>
     </row>
     <row r="7" ht="17" spans="1:4">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>37</v>
+        <v>68</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D7" s="8"/>
     </row>
     <row r="8" ht="17" spans="1:4">
       <c r="A8" s="5"/>
       <c r="B8" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>37</v>
+        <v>69</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D8" s="8"/>
     </row>
     <row r="9" ht="17" spans="1:4">
       <c r="A9" s="5"/>
       <c r="B9" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>37</v>
+        <v>70</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D9" s="8"/>
     </row>
     <row r="10" ht="17" spans="1:4">
       <c r="A10" s="5"/>
       <c r="B10" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>37</v>
+        <v>71</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D10" s="8"/>
     </row>
     <row r="11" ht="17" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="8"/>
@@ -2533,144 +2616,144 @@
     <row r="12" ht="17" spans="1:4">
       <c r="A12" s="5"/>
       <c r="B12" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>37</v>
+        <v>67</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D12" s="8"/>
     </row>
     <row r="13" ht="17" spans="1:4">
       <c r="A13" s="5"/>
       <c r="B13" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>37</v>
+        <v>68</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D13" s="8"/>
     </row>
     <row r="14" ht="17" spans="1:4">
       <c r="A14" s="5"/>
       <c r="B14" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>37</v>
+        <v>69</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D14" s="8"/>
     </row>
     <row r="15" ht="17" spans="1:4">
       <c r="A15" s="5"/>
       <c r="B15" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>37</v>
+        <v>71</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D15" s="8"/>
     </row>
     <row r="16" ht="17" spans="1:4">
       <c r="A16" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>30</v>
+        <v>75</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D16" s="8"/>
     </row>
     <row r="17" ht="17" spans="1:4">
       <c r="A17" s="5"/>
       <c r="B17" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>30</v>
+        <v>67</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D17" s="8"/>
     </row>
     <row r="18" ht="17" spans="1:4">
       <c r="A18" s="5"/>
       <c r="B18" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>30</v>
+        <v>68</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D18" s="8"/>
     </row>
     <row r="19" ht="17" spans="1:4">
       <c r="A19" s="5"/>
       <c r="B19" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>30</v>
+        <v>69</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D19" s="8"/>
     </row>
     <row r="20" ht="17" spans="1:4">
       <c r="A20" s="5"/>
       <c r="B20" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>30</v>
+        <v>71</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D20" s="8"/>
     </row>
     <row r="21" ht="17" spans="1:4">
       <c r="A21" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>30</v>
+        <v>75</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D21" s="8"/>
     </row>
     <row r="22" ht="17" spans="1:4">
       <c r="A22" s="5"/>
       <c r="B22" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>30</v>
+        <v>67</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D22" s="8"/>
     </row>
     <row r="23" ht="17" spans="1:4">
       <c r="A23" s="5"/>
       <c r="B23" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>30</v>
+        <v>68</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D23" s="8"/>
     </row>
     <row r="24" ht="17" spans="1:4">
       <c r="A24" s="5"/>
       <c r="B24" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>30</v>
+        <v>69</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D24" s="8"/>
     </row>
     <row r="25" ht="17" spans="1:4">
       <c r="A25" s="5"/>
       <c r="B25" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>30</v>
+        <v>71</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D25" s="8"/>
     </row>
@@ -2686,11 +2769,253 @@
     <mergeCell ref="A21:A25"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C25 C16:C19 C20:C24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C14 C15:C25">
       <formula1>"未进行,进行中,已暂停,已完成"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="3"/>
+  <cols>
+    <col min="2" max="2" width="102.567307692308" customWidth="1"/>
+    <col min="3" max="3" width="10.8942307692308" customWidth="1"/>
+    <col min="4" max="4" width="19.2211538461538" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="1:4">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" ht="17" spans="1:4">
+      <c r="A5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="8"/>
+    </row>
+    <row r="6" ht="17" spans="1:4">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
+    </row>
+    <row r="7" ht="17" spans="1:4">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="8"/>
+    </row>
+    <row r="8" ht="17" spans="1:4">
+      <c r="A8" s="5"/>
+      <c r="B8" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="8"/>
+    </row>
+    <row r="9" ht="17" spans="1:4">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="8"/>
+    </row>
+    <row r="10" ht="17" spans="1:4">
+      <c r="A10" s="5"/>
+      <c r="B10" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
+    </row>
+    <row r="11" ht="17" spans="1:4">
+      <c r="A11" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="8"/>
+    </row>
+    <row r="12" ht="17" spans="1:4">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="8"/>
+    </row>
+    <row r="13" ht="17" spans="1:4">
+      <c r="A13" s="5"/>
+      <c r="B13" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="8"/>
+    </row>
+    <row r="14" ht="17" spans="1:4">
+      <c r="A14" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
+    </row>
+    <row r="15" ht="17" spans="1:4">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="8"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="8"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="5"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="8"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="5"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
+    </row>
+    <row r="19" ht="17" spans="1:4">
+      <c r="A19" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="8"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="5"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="8"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="5"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="8"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="5"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="5"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="8"/>
+    </row>
+    <row r="24" ht="17" spans="1:4">
+      <c r="A24" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="5"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="5"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="5"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="5"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="A5:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="A19:A23"/>
+    <mergeCell ref="A24:A28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/file/personal/roleImportant/角色要事记录表_2026.xlsx
+++ b/file/personal/roleImportant/角色要事记录表_2026.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="95">
   <si>
     <t xml:space="preserve">角色</t>
   </si>
@@ -320,6 +320,14 @@
     <t xml:space="preserve">视频整理-完成到一半</t>
   </si>
   <si>
+    <t xml:space="preserve">【腾讯文档】鼻炎养护计划
+https://docs.qq.com/doc/DTHVSUk9NQ1VNZXp5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【腾讯文档】心脏养护方案
+https://docs.qq.com/doc/DTFJYYW5zcVpMVFNw</t>
+  </si>
+  <si>
     <t xml:space="preserve">医疗设备管理系统-技术方案</t>
   </si>
   <si>
@@ -349,7 +357,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -398,12 +406,6 @@
       <name val="Helvetica Neue"/>
       <family val="0"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="SimSun"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
@@ -561,7 +563,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -714,15 +716,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2255,30 +2253,34 @@
       </c>
       <c r="D13" s="16"/>
     </row>
-    <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="36"/>
       <c r="B14" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="16"/>
-    </row>
-    <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="36"/>
       <c r="B15" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="16"/>
+      <c r="C15" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="36"/>
       <c r="B16" s="37" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C16" s="19" t="s">
         <v>30</v>
@@ -2288,7 +2290,7 @@
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="36"/>
       <c r="B17" s="38" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C17" s="19" t="s">
         <v>30</v>
@@ -2297,10 +2299,10 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="36" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C18" s="19" t="s">
         <v>30</v>
@@ -2310,7 +2312,7 @@
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="36"/>
       <c r="B19" s="39" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C19" s="19" t="s">
         <v>30</v>
@@ -2319,8 +2321,8 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="36"/>
-      <c r="B20" s="40" t="s">
-        <v>91</v>
+      <c r="B20" s="38" t="s">
+        <v>93</v>
       </c>
       <c r="C20" s="19" t="s">
         <v>30</v>
@@ -2330,7 +2332,7 @@
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="36"/>
       <c r="B21" s="22" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C21" s="19" t="s">
         <v>30</v>
@@ -2349,15 +2351,19 @@
     <mergeCell ref="A18:A21"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C7:C10 C12" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C7:C10 C12 C14:C15" type="list">
       <formula1>"未进行,进行中,已暂停,已完成"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C11 C13:C21" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C11 C13 C16:C21" type="list">
       <formula1>"未进行,进行中,已暂停,已完成"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="D14" r:id="rId1" display="https://docs.qq.com/doc/DTHVSUk9NQ1VNZXp5"/>
+    <hyperlink ref="D15" r:id="rId2" display="https://docs.qq.com/doc/DTFJYYW5zcVpMVFNw"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/file/personal/roleImportant/角色要事记录表_2026.xlsx
+++ b/file/personal/roleImportant/角色要事记录表_2026.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="96">
   <si>
     <t xml:space="preserve">角色</t>
   </si>
@@ -318,6 +318,10 @@
   </si>
   <si>
     <t xml:space="preserve">视频整理-完成到一半</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【腾讯文档】皮肤保养方案
+https://docs.qq.com/doc/DTGtUSmRsVkxGV1RY</t>
   </si>
   <si>
     <t xml:space="preserve">【腾讯文档】鼻炎养护计划
@@ -2241,17 +2245,19 @@
       </c>
       <c r="D12" s="16"/>
     </row>
-    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="36" t="s">
         <v>74</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="16"/>
+      <c r="C13" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="36"/>
@@ -2262,7 +2268,7 @@
         <v>35</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2274,13 +2280,13 @@
         <v>35</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="36"/>
       <c r="B16" s="37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C16" s="19" t="s">
         <v>30</v>
@@ -2290,7 +2296,7 @@
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="36"/>
       <c r="B17" s="38" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C17" s="19" t="s">
         <v>30</v>
@@ -2299,10 +2305,10 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C18" s="19" t="s">
         <v>30</v>
@@ -2312,7 +2318,7 @@
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="36"/>
       <c r="B19" s="39" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C19" s="19" t="s">
         <v>30</v>
@@ -2322,7 +2328,7 @@
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="36"/>
       <c r="B20" s="38" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C20" s="19" t="s">
         <v>30</v>
@@ -2332,7 +2338,7 @@
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="36"/>
       <c r="B21" s="22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C21" s="19" t="s">
         <v>30</v>
@@ -2351,18 +2357,19 @@
     <mergeCell ref="A18:A21"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C7:C10 C12 C14:C15" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C7:C10 C12:C15" type="list">
       <formula1>"未进行,进行中,已暂停,已完成"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C11 C13 C16:C21" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C11 C16:C21" type="list">
       <formula1>"未进行,进行中,已暂停,已完成"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D14" r:id="rId1" display="https://docs.qq.com/doc/DTHVSUk9NQ1VNZXp5"/>
-    <hyperlink ref="D15" r:id="rId2" display="https://docs.qq.com/doc/DTFJYYW5zcVpMVFNw"/>
+    <hyperlink ref="D13" r:id="rId1" display="https://docs.qq.com/doc/DTGtUSmRsVkxGV1RY"/>
+    <hyperlink ref="D14" r:id="rId2" display="【腾讯文档】鼻炎养护计划&#10;https://docs.qq.com/doc/DTHVSUk9NQ1VNZXp5"/>
+    <hyperlink ref="D15" r:id="rId3" display="【腾讯文档】心脏养护方案&#10;https://docs.qq.com/doc/DTFJYYW5zcVpMVFNw"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/file/personal/roleImportant/角色要事记录表_2026.xlsx
+++ b/file/personal/roleImportant/角色要事记录表_2026.xlsx
@@ -291,10 +291,11 @@
   </si>
   <si>
     <t>关于学习资料整理
-1、视频资料
-2、教材文档资料
-3、纸质实物资料
-4、日常资料文档</t>
+- 培训资料--视频(数量全对,需核对结尾+声音)
+- 培训资料--视频对应电子文档
+- 培训资料--题库
+- 培训资料--教材纸质书籍
+- 日常资料文档</t>
   </si>
   <si>
     <t>家庭保险配置</t>
@@ -1133,10 +1134,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2107,7 +2108,7 @@
       <c r="C2" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E2" s="9"/>
@@ -2120,7 +2121,7 @@
       <c r="C3" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E3" s="9"/>
@@ -2133,7 +2134,7 @@
       <c r="C4" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E4" s="9"/>
@@ -2226,7 +2227,7 @@
       <c r="C11" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E11" s="9"/>
@@ -2239,7 +2240,7 @@
       <c r="C12" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E12" s="9"/>
@@ -2252,7 +2253,7 @@
       <c r="C13" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E13" s="9"/>
@@ -2267,7 +2268,7 @@
       <c r="C14" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E14" s="9"/>
@@ -2280,7 +2281,7 @@
       <c r="C15" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E15" s="9"/>
@@ -2293,7 +2294,7 @@
       <c r="C16" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E16" s="9"/>
@@ -2306,7 +2307,7 @@
       <c r="C17" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E17" s="9"/>
@@ -2321,7 +2322,7 @@
       <c r="C18" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="12" t="s">
         <v>51</v>
       </c>
       <c r="E18" s="9" t="s">
@@ -2336,7 +2337,7 @@
       <c r="C19" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E19" s="9"/>
@@ -2362,7 +2363,7 @@
       <c r="C21" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E21" s="9"/>
@@ -2375,7 +2376,7 @@
       <c r="C22" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E22" s="9"/>
@@ -2388,7 +2389,7 @@
       <c r="C23" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="9"/>
@@ -2403,7 +2404,7 @@
       <c r="C24" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E24" s="9"/>
@@ -3061,7 +3062,7 @@
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" ht="94.75" customHeight="1" spans="1:4">
+    <row r="2" ht="105" customHeight="1" spans="1:4">
       <c r="A2" s="2"/>
       <c r="B2" s="4" t="s">
         <v>76</v>
@@ -3218,18 +3219,18 @@
       <c r="B16" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>30</v>
+      <c r="C16" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="D16" s="9"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="8"/>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="11" t="s">
-        <v>30</v>
+      <c r="C17" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="D17" s="9"/>
     </row>
@@ -3237,10 +3238,10 @@
       <c r="A18" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="12" t="s">
         <v>30</v>
       </c>
       <c r="D18" s="13"/>
@@ -3250,17 +3251,17 @@
       <c r="B19" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="12" t="s">
         <v>30</v>
       </c>
       <c r="D19" s="13"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="8"/>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="12" t="s">
         <v>30</v>
       </c>
       <c r="D20" s="13"/>
@@ -3270,7 +3271,7 @@
       <c r="B21" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="12" t="s">
         <v>30</v>
       </c>
       <c r="D21" s="13"/>
@@ -3285,7 +3286,7 @@
     <mergeCell ref="A18:A21"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3 C5 C11 C7:C10 C12:C15 C16:C21">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3 C5 C16 C17 C7:C15 C18:C21">
       <formula1>"未进行,进行中,已暂停,已完成"</formula1>
     </dataValidation>
   </dataValidations>

--- a/file/personal/roleImportant/角色要事记录表_2026.xlsx
+++ b/file/personal/roleImportant/角色要事记录表_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="角色目录" sheetId="1" state="visible" r:id="rId2"/>
@@ -13,9 +13,10 @@
     <sheet name="一月" sheetId="3" state="visible" r:id="rId4"/>
     <sheet name="二月" sheetId="4" state="visible" r:id="rId5"/>
     <sheet name="四月" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="五月" sheetId="6" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">待办任务!$A$1:$D$24</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">待办任务!$A$1:$D$23</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="106">
   <si>
     <t xml:space="preserve">角色</t>
   </si>
@@ -189,9 +190,6 @@
   </si>
   <si>
     <t xml:space="preserve">每一个月做一次反思，看这个月有没有在能力、素养、工作、家庭、职业发展、目标实现等等各个方面有成长或进展？以及问题出在哪里？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">去成都旅游/重庆/海南全家旅游一次</t>
   </si>
   <si>
     <r>
@@ -304,6 +302,7 @@
         <color rgb="FF000000"/>
         <rFont val="SimSun"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">-完成
 </t>
@@ -324,6 +323,7 @@
         <color rgb="FF000000"/>
         <rFont val="SimSun"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">-完成
 </t>
@@ -344,6 +344,7 @@
         <color rgb="FF000000"/>
         <rFont val="SimSun"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">-完成
 </t>
@@ -364,6 +365,7 @@
         <color rgb="FF000000"/>
         <rFont val="SimSun"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">-完成</t>
     </r>
@@ -427,6 +429,39 @@
   </si>
   <si>
     <t xml:space="preserve">去掉脸上斑点、痘痘-去医院（可以预约五一期间）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">为参加6.6号上海市大数据中心考试做准备</t>
+  </si>
+  <si>
+    <t xml:space="preserve">核心基础知识：1遍（职测）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不包括资料分析</t>
+  </si>
+  <si>
+    <t xml:space="preserve">核心基础知识：2遍（职测）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">核心基础知识：3遍（职测）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">核心基础知识：4遍（职测）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">核心基础知识：5遍（职测）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">收集整理专业知识预测考题</t>
+  </si>
+  <si>
+    <t xml:space="preserve">专业知识预测考题：写1遍</t>
+  </si>
+  <si>
+    <t xml:space="preserve">购买专业的职测刷题卷</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每天20题</t>
   </si>
 </sst>
 </file>
@@ -492,13 +527,13 @@
       <color rgb="FF000000"/>
       <name val="SimSun"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="SimSun"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="11">
@@ -649,7 +684,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -798,16 +833,20 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1208,7 +1247,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E1048576"/>
   <sheetFormatPr defaultColWidth="16.359375" defaultRowHeight="16.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.36"/>
@@ -1364,8 +1403,8 @@
       <c r="C11" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="19" t="s">
-        <v>30</v>
+      <c r="D11" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E11" s="16"/>
     </row>
@@ -1418,8 +1457,8 @@
       <c r="C15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="19" t="s">
-        <v>30</v>
+      <c r="D15" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E15" s="16"/>
     </row>
@@ -1431,8 +1470,8 @@
       <c r="C16" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="19" t="s">
-        <v>30</v>
+      <c r="D16" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E16" s="16"/>
     </row>
@@ -1444,8 +1483,8 @@
       <c r="C17" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="19" t="s">
-        <v>30</v>
+      <c r="D17" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E17" s="16"/>
     </row>
@@ -1479,33 +1518,33 @@
       </c>
       <c r="E19" s="16"/>
     </row>
-    <row r="20" customFormat="false" ht="13" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="28"/>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="23" t="s">
-        <v>35</v>
+      <c r="C20" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="E20" s="16"/>
     </row>
-    <row r="21" customFormat="false" ht="16.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="28"/>
       <c r="B21" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>30</v>
+      <c r="C21" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="E21" s="16"/>
     </row>
-    <row r="22" customFormat="false" ht="16.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="28"/>
       <c r="B22" s="24" t="s">
         <v>56</v>
@@ -1518,10 +1557,12 @@
       </c>
       <c r="E22" s="16"/>
     </row>
-    <row r="23" customFormat="false" ht="16.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="28"/>
-      <c r="B23" s="24" t="s">
+    <row r="23" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="29" t="s">
         <v>57</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>58</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>22</v>
@@ -1531,20 +1572,8 @@
       </c>
       <c r="E23" s="16"/>
     </row>
-    <row r="24" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="B24" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E24" s="16"/>
+    <row r="24" customFormat="false" ht="16.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="31"/>
     </row>
     <row r="25" customFormat="false" ht="16.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="31"/>
@@ -1552,19 +1581,17 @@
     <row r="26" customFormat="false" ht="16.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="31"/>
     </row>
-    <row r="27" customFormat="false" ht="16.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="31"/>
-    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A1:D24"/>
+  <autoFilter ref="A1:D23"/>
   <mergeCells count="4">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A13"/>
     <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A23"/>
+    <mergeCell ref="A18:A22"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D2:D24" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D2:D23" type="list">
       <formula1>"未进行,进行中,已暂停,已完成"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1595,10 +1622,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="33" t="s">
         <v>60</v>
-      </c>
-      <c r="B1" s="33" t="s">
-        <v>61</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -1617,22 +1644,22 @@
     </row>
     <row r="4" customFormat="false" ht="16.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B4" s="35"/>
       <c r="C4" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="34" t="s">
         <v>63</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="22" t="s">
         <v>65</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>66</v>
       </c>
       <c r="C5" s="23" t="s">
         <v>35</v>
@@ -1642,7 +1669,7 @@
     <row r="6" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="36"/>
       <c r="B6" s="22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C6" s="23" t="s">
         <v>35</v>
@@ -1652,7 +1679,7 @@
     <row r="7" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="36"/>
       <c r="B7" s="22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>30</v>
@@ -1662,7 +1689,7 @@
     <row r="8" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="36"/>
       <c r="B8" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C8" s="23" t="s">
         <v>35</v>
@@ -1672,7 +1699,7 @@
     <row r="9" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="36"/>
       <c r="B9" s="22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>30</v>
@@ -1682,7 +1709,7 @@
     <row r="10" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36"/>
       <c r="B10" s="22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>30</v>
@@ -1691,10 +1718,10 @@
     </row>
     <row r="11" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C11" s="23" t="s">
         <v>35</v>
@@ -1704,7 +1731,7 @@
     <row r="12" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="36"/>
       <c r="B12" s="22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C12" s="23" t="s">
         <v>35</v>
@@ -1714,7 +1741,7 @@
     <row r="13" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="36"/>
       <c r="B13" s="22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>30</v>
@@ -1724,7 +1751,7 @@
     <row r="14" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="36"/>
       <c r="B14" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C14" s="23" t="s">
         <v>35</v>
@@ -1734,7 +1761,7 @@
     <row r="15" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="36"/>
       <c r="B15" s="22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C15" s="23" t="s">
         <v>35</v>
@@ -1744,7 +1771,7 @@
     <row r="16" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="36"/>
       <c r="B16" s="22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C16" s="23" t="s">
         <v>35</v>
@@ -1753,10 +1780,10 @@
     </row>
     <row r="17" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="36" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C17" s="23" t="s">
         <v>35</v>
@@ -1766,7 +1793,7 @@
     <row r="18" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="36"/>
       <c r="B18" s="22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C18" s="23" t="s">
         <v>35</v>
@@ -1776,7 +1803,7 @@
     <row r="19" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="36"/>
       <c r="B19" s="22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>30</v>
@@ -1786,7 +1813,7 @@
     <row r="20" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="36"/>
       <c r="B20" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C20" s="23" t="s">
         <v>35</v>
@@ -1796,7 +1823,7 @@
     <row r="21" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="36"/>
       <c r="B21" s="22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C21" s="23" t="s">
         <v>35</v>
@@ -1806,7 +1833,7 @@
     <row r="22" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="36"/>
       <c r="B22" s="22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C22" s="23" t="s">
         <v>35</v>
@@ -1815,10 +1842,10 @@
     </row>
     <row r="23" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="36" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C23" s="23" t="s">
         <v>35</v>
@@ -1828,7 +1855,7 @@
     <row r="24" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="36"/>
       <c r="B24" s="22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C24" s="23" t="s">
         <v>35</v>
@@ -1838,7 +1865,7 @@
     <row r="25" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="36"/>
       <c r="B25" s="22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C25" s="23" t="s">
         <v>35</v>
@@ -1848,7 +1875,7 @@
     <row r="26" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="36"/>
       <c r="B26" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C26" s="23" t="s">
         <v>35</v>
@@ -1858,7 +1885,7 @@
     <row r="27" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="36"/>
       <c r="B27" s="22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C27" s="23" t="s">
         <v>35</v>
@@ -1868,7 +1895,7 @@
     <row r="28" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="36"/>
       <c r="B28" s="22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C28" s="23" t="s">
         <v>35</v>
@@ -1917,10 +1944,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="33" t="s">
         <v>60</v>
-      </c>
-      <c r="B1" s="33" t="s">
-        <v>61</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -1939,22 +1966,22 @@
     </row>
     <row r="4" customFormat="false" ht="16.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B4" s="35"/>
       <c r="C4" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="34" t="s">
         <v>63</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="22" t="s">
         <v>65</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>66</v>
       </c>
       <c r="C5" s="23" t="s">
         <v>35</v>
@@ -1964,7 +1991,7 @@
     <row r="6" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="36"/>
       <c r="B6" s="22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C6" s="23" t="s">
         <v>35</v>
@@ -1974,7 +2001,7 @@
     <row r="7" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="36"/>
       <c r="B7" s="22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>35</v>
@@ -1984,7 +2011,7 @@
     <row r="8" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="36"/>
       <c r="B8" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C8" s="23" t="s">
         <v>35</v>
@@ -1994,7 +2021,7 @@
     <row r="9" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="36"/>
       <c r="B9" s="22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" s="23" t="s">
         <v>35</v>
@@ -2004,7 +2031,7 @@
     <row r="10" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36"/>
       <c r="B10" s="22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" s="23" t="s">
         <v>35</v>
@@ -2013,10 +2040,10 @@
     </row>
     <row r="11" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>30</v>
@@ -2026,7 +2053,7 @@
     <row r="12" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="36"/>
       <c r="B12" s="22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C12" s="23" t="s">
         <v>35</v>
@@ -2036,7 +2063,7 @@
     <row r="13" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="36"/>
       <c r="B13" s="22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C13" s="23" t="s">
         <v>35</v>
@@ -2046,7 +2073,7 @@
     <row r="14" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="36"/>
       <c r="B14" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C14" s="23" t="s">
         <v>35</v>
@@ -2056,7 +2083,7 @@
     <row r="15" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="36"/>
       <c r="B15" s="22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C15" s="23" t="s">
         <v>35</v>
@@ -2065,10 +2092,10 @@
     </row>
     <row r="16" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="36" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C16" s="23" t="s">
         <v>35</v>
@@ -2078,7 +2105,7 @@
     <row r="17" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="36"/>
       <c r="B17" s="22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C17" s="23" t="s">
         <v>35</v>
@@ -2088,7 +2115,7 @@
     <row r="18" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="36"/>
       <c r="B18" s="22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C18" s="23" t="s">
         <v>35</v>
@@ -2098,7 +2125,7 @@
     <row r="19" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="36"/>
       <c r="B19" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C19" s="23" t="s">
         <v>35</v>
@@ -2108,7 +2135,7 @@
     <row r="20" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="36"/>
       <c r="B20" s="22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C20" s="23" t="s">
         <v>35</v>
@@ -2117,10 +2144,10 @@
     </row>
     <row r="21" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="22" t="s">
         <v>74</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>75</v>
       </c>
       <c r="C21" s="23" t="s">
         <v>35</v>
@@ -2130,7 +2157,7 @@
     <row r="22" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="36"/>
       <c r="B22" s="22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C22" s="23" t="s">
         <v>35</v>
@@ -2140,7 +2167,7 @@
     <row r="23" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="36"/>
       <c r="B23" s="22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C23" s="23" t="s">
         <v>35</v>
@@ -2150,7 +2177,7 @@
     <row r="24" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="36"/>
       <c r="B24" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C24" s="23" t="s">
         <v>35</v>
@@ -2160,7 +2187,7 @@
     <row r="25" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="36"/>
       <c r="B25" s="22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C25" s="23" t="s">
         <v>35</v>
@@ -2209,10 +2236,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="33" t="s">
         <v>60</v>
-      </c>
-      <c r="B1" s="33" t="s">
-        <v>61</v>
       </c>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
@@ -2220,7 +2247,7 @@
     <row r="2" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="21"/>
       <c r="B2" s="22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" s="23" t="s">
         <v>35</v>
@@ -2230,7 +2257,7 @@
     <row r="3" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21"/>
       <c r="B3" s="33" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" s="23" t="s">
         <v>35</v>
@@ -2240,7 +2267,7 @@
     <row r="4" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21"/>
       <c r="B4" s="33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C4" s="23" t="s">
         <v>35</v>
@@ -2250,7 +2277,7 @@
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21"/>
       <c r="B5" s="22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C5" s="23" t="s">
         <v>35</v>
@@ -2259,22 +2286,22 @@
     </row>
     <row r="6" customFormat="false" ht="16.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B6" s="35"/>
       <c r="C6" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="34" t="s">
         <v>63</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>35</v>
@@ -2284,7 +2311,7 @@
     <row r="8" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="36"/>
       <c r="B8" s="22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C8" s="23" t="s">
         <v>35</v>
@@ -2293,10 +2320,10 @@
     </row>
     <row r="9" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C9" s="23" t="s">
         <v>35</v>
@@ -2305,10 +2332,10 @@
     </row>
     <row r="10" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10" s="23" t="s">
         <v>35</v>
@@ -2318,7 +2345,7 @@
     <row r="11" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="36"/>
       <c r="B11" s="22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C11" s="23" t="s">
         <v>35</v>
@@ -2328,7 +2355,7 @@
     <row r="12" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="36"/>
       <c r="B12" s="22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C12" s="23" t="s">
         <v>35</v>
@@ -2337,7 +2364,7 @@
     </row>
     <row r="13" customFormat="false" ht="84" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="36" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>46</v>
@@ -2346,7 +2373,7 @@
         <v>35</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="84" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2358,7 +2385,7 @@
         <v>35</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="84" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2370,13 +2397,13 @@
         <v>35</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="36"/>
       <c r="B16" s="37" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C16" s="23" t="s">
         <v>35</v>
@@ -2386,7 +2413,7 @@
     <row r="17" customFormat="false" ht="16.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="36"/>
       <c r="B17" s="38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C17" s="23" t="s">
         <v>35</v>
@@ -2395,10 +2422,10 @@
     </row>
     <row r="18" customFormat="false" ht="16.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="38" t="s">
         <v>91</v>
-      </c>
-      <c r="B18" s="38" t="s">
-        <v>92</v>
       </c>
       <c r="C18" s="23" t="s">
         <v>35</v>
@@ -2408,7 +2435,7 @@
     <row r="19" customFormat="false" ht="16.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="36"/>
       <c r="B19" s="39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C19" s="23" t="s">
         <v>35</v>
@@ -2418,7 +2445,7 @@
     <row r="20" customFormat="false" ht="16.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="36"/>
       <c r="B20" s="38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C20" s="23" t="s">
         <v>35</v>
@@ -2428,7 +2455,7 @@
     <row r="21" customFormat="false" ht="17" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="36"/>
       <c r="B21" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C21" s="19" t="s">
         <v>30</v>
@@ -2463,4 +2490,224 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="9.23046875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="32" width="102.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="32" width="10.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="32" width="19.22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+    </row>
+    <row r="2" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="21"/>
+      <c r="B2" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="22"/>
+    </row>
+    <row r="3" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="21"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="33"/>
+    </row>
+    <row r="4" customFormat="false" ht="16.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="36"/>
+      <c r="B6" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="36"/>
+      <c r="B7" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="36"/>
+      <c r="B8" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="36"/>
+      <c r="B9" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="36"/>
+      <c r="B10" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="16"/>
+    </row>
+    <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="36"/>
+      <c r="B11" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="16"/>
+    </row>
+    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="36"/>
+      <c r="B12" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="16"/>
+    </row>
+    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="36"/>
+      <c r="B13" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="16"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="22"/>
+      <c r="C14" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="22"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="36"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="22"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="36"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="22"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="36"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="16"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="36"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="A5:A13"/>
+    <mergeCell ref="A14:A18"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C2:C3 C5:C18" type="list">
+      <formula1>"未进行,进行中,已暂停,已完成"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/file/personal/roleImportant/角色要事记录表_2026.xlsx
+++ b/file/personal/roleImportant/角色要事记录表_2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22980" windowHeight="13160" tabRatio="500" activeTab="5"/>
+    <workbookView windowWidth="22980" windowHeight="13160" tabRatio="500" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="角色目录" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="二月" sheetId="4" r:id="rId4"/>
     <sheet name="四月" sheetId="5" r:id="rId5"/>
     <sheet name="五月" sheetId="6" r:id="rId6"/>
+    <sheet name="六月" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">待办任务!$A$1:$D$23</definedName>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="121">
   <si>
     <t>角色</t>
   </si>
@@ -464,12 +465,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
       <t>周三:数量5图形5推理</t>
     </r>
     <r>
@@ -701,6 +696,27 @@
   </si>
   <si>
     <t>专业知识预测考题写：1遍</t>
+  </si>
+  <si>
+    <t>周一:数量5图形5推理5言语10常识2</t>
+  </si>
+  <si>
+    <t>周二:数量5图形5推理5言语10常识2</t>
+  </si>
+  <si>
+    <t>周三:数量5图形5推理5言语10常识2</t>
+  </si>
+  <si>
+    <t>周四:数量5图形5推理5言语10常识2</t>
+  </si>
+  <si>
+    <t>周五:数量5图形5推理5言语10常识2</t>
+  </si>
+  <si>
+    <t>专业知识预测考题读：2遍</t>
+  </si>
+  <si>
+    <t>专业知识预测考题读：3遍</t>
   </si>
 </sst>
 </file>
@@ -1166,7 +1182,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1184,6 +1200,43 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -1333,7 +1386,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1345,34 +1398,34 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1457,7 +1510,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1482,22 +1535,31 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1563,19 +1625,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2185,231 +2247,231 @@
   <dimension ref="A1:E30"/>
   <sheetFormatPr defaultColWidth="6" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="14.4134615384615" style="16" customWidth="1"/>
-    <col min="2" max="16384" width="6" style="16"/>
+    <col min="1" max="1" width="14.4134615384615" style="19" customWidth="1"/>
+    <col min="2" max="16384" width="6" style="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="14" customHeight="1" spans="1:5">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
     </row>
     <row r="2" ht="14" customHeight="1" spans="1:5">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
     </row>
     <row r="3" ht="14" customHeight="1" spans="1:5">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
     </row>
     <row r="4" ht="14" customHeight="1" spans="1:5">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
     </row>
     <row r="5" ht="14" customHeight="1" spans="1:5">
-      <c r="A5" s="39"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
+      <c r="A5" s="42"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
     </row>
     <row r="6" ht="14" customHeight="1" spans="1:5">
-      <c r="A6" s="39"/>
-      <c r="B6" s="36"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
+      <c r="A6" s="42"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
     </row>
     <row r="7" ht="14" customHeight="1" spans="1:5">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
     </row>
     <row r="8" ht="14" customHeight="1" spans="1:5">
-      <c r="A8" s="39"/>
-      <c r="B8" s="36"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
+      <c r="A8" s="42"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
     </row>
     <row r="9" ht="14" customHeight="1" spans="1:5">
-      <c r="A9" s="39"/>
-      <c r="B9" s="36"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
+      <c r="A9" s="42"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
     </row>
     <row r="10" ht="14" customHeight="1" spans="1:5">
-      <c r="A10" s="39" t="s">
+      <c r="A10" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="36"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
     </row>
     <row r="11" ht="14" customHeight="1" spans="1:5">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="36"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
     </row>
     <row r="12" ht="14" customHeight="1" spans="1:5">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="36"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
     </row>
     <row r="13" ht="14" customHeight="1" spans="1:5">
-      <c r="A13" s="39" t="s">
+      <c r="A13" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="36"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
     </row>
     <row r="14" ht="14" customHeight="1" spans="1:5">
-      <c r="A14" s="39" t="s">
+      <c r="A14" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
     </row>
     <row r="15" ht="14" customHeight="1" spans="1:5">
-      <c r="A15" s="39" t="s">
+      <c r="A15" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
     </row>
     <row r="16" ht="14" customHeight="1" spans="1:5">
-      <c r="A16" s="39" t="s">
+      <c r="A16" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="36"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
     </row>
     <row r="17" ht="14" customHeight="1" spans="1:5">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="36"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
     </row>
     <row r="18" ht="14" customHeight="1" spans="1:5">
-      <c r="A18" s="39" t="s">
+      <c r="A18" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="36"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
     </row>
     <row r="19" ht="14" customHeight="1" spans="1:5">
-      <c r="A19" s="39" t="s">
+      <c r="A19" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="36"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
     </row>
     <row r="20" ht="14" customHeight="1" spans="1:5">
-      <c r="A20" s="39" t="s">
+      <c r="A20" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="36"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
     </row>
     <row r="21" ht="14" customHeight="1" spans="1:5">
-      <c r="A21" s="39" t="s">
+      <c r="A21" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="36"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
     </row>
     <row r="22" ht="14" customHeight="1" spans="1:5">
-      <c r="A22" s="39" t="s">
+      <c r="A22" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="36"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
     </row>
     <row r="23" ht="14" customHeight="1" spans="1:5">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
     </row>
     <row r="26" ht="13.5" customHeight="1" spans="1:5">
-      <c r="A26" s="40" t="s">
+      <c r="A26" s="43" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="27" ht="13.5" customHeight="1" spans="1:5">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="26" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="28" ht="13.5" customHeight="1" spans="1:5">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="32" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="29" ht="13.5" customHeight="1" spans="1:5">
-      <c r="A29" s="26" t="s">
+      <c r="A29" s="29" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="30" ht="13.5" customHeight="1" spans="1:5">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="16" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2434,38 +2496,38 @@
   <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="16.3557692307692" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="16.3557692307692" style="16"/>
-    <col min="2" max="2" width="99.1153846153846" style="17" customWidth="1"/>
-    <col min="3" max="3" width="14.0961538461538" style="17" customWidth="1"/>
-    <col min="4" max="4" width="16.3557692307692" style="16"/>
-    <col min="5" max="5" width="18.2692307692308" style="16" customWidth="1"/>
-    <col min="6" max="6" width="17.7788461538462" style="16" customWidth="1"/>
-    <col min="7" max="16384" width="16.3557692307692" style="16"/>
+    <col min="1" max="1" width="16.3557692307692" style="19"/>
+    <col min="2" max="2" width="99.1153846153846" style="20" customWidth="1"/>
+    <col min="3" max="3" width="14.0961538461538" style="20" customWidth="1"/>
+    <col min="4" max="4" width="16.3557692307692" style="19"/>
+    <col min="5" max="5" width="18.2692307692308" style="19" customWidth="1"/>
+    <col min="6" max="6" width="17.7788461538462" style="19" customWidth="1"/>
+    <col min="7" max="16384" width="16.3557692307692" style="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.55" customHeight="1" spans="1:5">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="23" t="s">
         <v>27</v>
       </c>
       <c r="E1" s="10"/>
     </row>
     <row r="2" ht="13.35" customHeight="1" spans="1:5">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="26" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -2474,11 +2536,11 @@
       <c r="E2" s="10"/>
     </row>
     <row r="3" ht="13.35" customHeight="1" spans="1:5">
-      <c r="A3" s="21"/>
-      <c r="B3" s="22" t="s">
+      <c r="A3" s="24"/>
+      <c r="B3" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="26" t="s">
         <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -2487,11 +2549,11 @@
       <c r="E3" s="10"/>
     </row>
     <row r="4" ht="13.35" customHeight="1" spans="1:5">
-      <c r="A4" s="21"/>
-      <c r="B4" s="24" t="s">
+      <c r="A4" s="24"/>
+      <c r="B4" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="26" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="5" t="s">
@@ -2506,7 +2568,7 @@
       <c r="B5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="16" t="s">
         <v>23</v>
       </c>
       <c r="D5" s="9" t="s">
@@ -2519,7 +2581,7 @@
       <c r="B6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="16" t="s">
         <v>23</v>
       </c>
       <c r="D6" s="9" t="s">
@@ -2532,7 +2594,7 @@
       <c r="B7" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="16" t="s">
         <v>23</v>
       </c>
       <c r="D7" s="9" t="s">
@@ -2545,7 +2607,7 @@
       <c r="B8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="16" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="9" t="s">
@@ -2558,7 +2620,7 @@
       <c r="B9" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="16" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="9" t="s">
@@ -2571,7 +2633,7 @@
       <c r="B10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="16" t="s">
         <v>23</v>
       </c>
       <c r="D10" s="9" t="s">
@@ -2581,10 +2643,10 @@
     </row>
     <row r="11" ht="13" customHeight="1" spans="1:5">
       <c r="A11" s="2"/>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="29" t="s">
         <v>22</v>
       </c>
       <c r="D11" s="9" t="s">
@@ -2594,10 +2656,10 @@
     </row>
     <row r="12" ht="13" customHeight="1" spans="1:5">
       <c r="A12" s="2"/>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="29" t="s">
         <v>22</v>
       </c>
       <c r="D12" s="5" t="s">
@@ -2607,10 +2669,10 @@
     </row>
     <row r="13" ht="13" customHeight="1" spans="1:5">
       <c r="A13" s="2"/>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="29" t="s">
         <v>22</v>
       </c>
       <c r="D13" s="5" t="s">
@@ -2622,10 +2684,10 @@
       <c r="A14" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="32" t="s">
         <v>21</v>
       </c>
       <c r="D14" s="5" t="s">
@@ -2635,10 +2697,10 @@
     </row>
     <row r="15" ht="13" customHeight="1" spans="1:5">
       <c r="A15" s="2"/>
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" s="32" t="s">
         <v>21</v>
       </c>
       <c r="D15" s="9" t="s">
@@ -2648,10 +2710,10 @@
     </row>
     <row r="16" ht="13" customHeight="1" spans="1:5">
       <c r="A16" s="2"/>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" s="32" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="9" t="s">
@@ -2661,10 +2723,10 @@
     </row>
     <row r="17" ht="13" customHeight="1" spans="1:5">
       <c r="A17" s="2"/>
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="32" t="s">
         <v>21</v>
       </c>
       <c r="D17" s="9" t="s">
@@ -2673,13 +2735,13 @@
       <c r="E17" s="10"/>
     </row>
     <row r="18" ht="13" customHeight="1" spans="1:5">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="34" t="s">
         <v>49</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="29" t="s">
         <v>22</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -2690,11 +2752,11 @@
       </c>
     </row>
     <row r="19" ht="13" customHeight="1" spans="1:5">
-      <c r="A19" s="31"/>
+      <c r="A19" s="34"/>
       <c r="B19" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="29" t="s">
         <v>22</v>
       </c>
       <c r="D19" s="5" t="s">
@@ -2703,11 +2765,11 @@
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="31"/>
-      <c r="B20" s="25" t="s">
+      <c r="A20" s="34"/>
+      <c r="B20" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" s="32" t="s">
         <v>21</v>
       </c>
       <c r="D20" s="5" t="s">
@@ -2716,11 +2778,11 @@
       <c r="E20" s="10"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="31"/>
-      <c r="B21" s="25" t="s">
+      <c r="A21" s="34"/>
+      <c r="B21" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="29" t="s">
         <v>22</v>
       </c>
       <c r="D21" s="9" t="s">
@@ -2729,11 +2791,11 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="31"/>
-      <c r="B22" s="25" t="s">
+      <c r="A22" s="34"/>
+      <c r="B22" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="29" t="s">
         <v>22</v>
       </c>
       <c r="D22" s="5" t="s">
@@ -2742,13 +2804,13 @@
       <c r="E22" s="10"/>
     </row>
     <row r="23" ht="17" spans="1:5">
-      <c r="A23" s="32" t="s">
+      <c r="A23" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="29" t="s">
         <v>22</v>
       </c>
       <c r="D23" s="5" t="s">
@@ -2757,13 +2819,13 @@
       <c r="E23" s="10"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="B24" s="34"/>
+      <c r="B24" s="37"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="B25" s="34"/>
+      <c r="B25" s="37"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="B26" s="34"/>
+      <c r="B26" s="37"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D23" etc:filterBottomFollowUsedRange="0">
@@ -2834,7 +2896,7 @@
       </c>
     </row>
     <row r="5" ht="17" spans="1:4">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="15" t="s">
         <v>64</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -2846,7 +2908,7 @@
       <c r="D5" s="10"/>
     </row>
     <row r="6" ht="17" spans="1:4">
-      <c r="A6" s="8"/>
+      <c r="A6" s="15"/>
       <c r="B6" s="4" t="s">
         <v>66</v>
       </c>
@@ -2856,17 +2918,17 @@
       <c r="D6" s="10"/>
     </row>
     <row r="7" ht="17" spans="1:4">
-      <c r="A7" s="8"/>
+      <c r="A7" s="15"/>
       <c r="B7" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="10"/>
     </row>
     <row r="8" ht="17" spans="1:4">
-      <c r="A8" s="8"/>
+      <c r="A8" s="15"/>
       <c r="B8" s="4" t="s">
         <v>68</v>
       </c>
@@ -2876,27 +2938,27 @@
       <c r="D8" s="10"/>
     </row>
     <row r="9" ht="17" spans="1:4">
-      <c r="A9" s="8"/>
+      <c r="A9" s="15"/>
       <c r="B9" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D9" s="10"/>
     </row>
     <row r="10" ht="17" spans="1:4">
-      <c r="A10" s="8"/>
+      <c r="A10" s="15"/>
       <c r="B10" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="10"/>
     </row>
     <row r="11" ht="17" spans="1:4">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="15" t="s">
         <v>71</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -2908,7 +2970,7 @@
       <c r="D11" s="10"/>
     </row>
     <row r="12" ht="17" spans="1:4">
-      <c r="A12" s="8"/>
+      <c r="A12" s="15"/>
       <c r="B12" s="4" t="s">
         <v>66</v>
       </c>
@@ -2918,17 +2980,17 @@
       <c r="D12" s="10"/>
     </row>
     <row r="13" ht="17" spans="1:4">
-      <c r="A13" s="8"/>
+      <c r="A13" s="15"/>
       <c r="B13" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D13" s="10"/>
     </row>
     <row r="14" ht="17" spans="1:4">
-      <c r="A14" s="8"/>
+      <c r="A14" s="15"/>
       <c r="B14" s="4" t="s">
         <v>68</v>
       </c>
@@ -2938,7 +3000,7 @@
       <c r="D14" s="10"/>
     </row>
     <row r="15" ht="17" spans="1:4">
-      <c r="A15" s="8"/>
+      <c r="A15" s="15"/>
       <c r="B15" s="4" t="s">
         <v>69</v>
       </c>
@@ -2948,7 +3010,7 @@
       <c r="D15" s="10"/>
     </row>
     <row r="16" ht="17" spans="1:4">
-      <c r="A16" s="8"/>
+      <c r="A16" s="15"/>
       <c r="B16" s="4" t="s">
         <v>70</v>
       </c>
@@ -2958,7 +3020,7 @@
       <c r="D16" s="10"/>
     </row>
     <row r="17" ht="17" spans="1:4">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="15" t="s">
         <v>72</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -2970,7 +3032,7 @@
       <c r="D17" s="10"/>
     </row>
     <row r="18" ht="17" spans="1:4">
-      <c r="A18" s="8"/>
+      <c r="A18" s="15"/>
       <c r="B18" s="4" t="s">
         <v>66</v>
       </c>
@@ -2980,17 +3042,17 @@
       <c r="D18" s="10"/>
     </row>
     <row r="19" ht="17" spans="1:4">
-      <c r="A19" s="8"/>
+      <c r="A19" s="15"/>
       <c r="B19" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D19" s="10"/>
     </row>
     <row r="20" ht="17" spans="1:4">
-      <c r="A20" s="8"/>
+      <c r="A20" s="15"/>
       <c r="B20" s="4" t="s">
         <v>68</v>
       </c>
@@ -3000,7 +3062,7 @@
       <c r="D20" s="10"/>
     </row>
     <row r="21" ht="17" spans="1:4">
-      <c r="A21" s="8"/>
+      <c r="A21" s="15"/>
       <c r="B21" s="4" t="s">
         <v>69</v>
       </c>
@@ -3010,7 +3072,7 @@
       <c r="D21" s="10"/>
     </row>
     <row r="22" ht="17" spans="1:4">
-      <c r="A22" s="8"/>
+      <c r="A22" s="15"/>
       <c r="B22" s="4" t="s">
         <v>70</v>
       </c>
@@ -3020,7 +3082,7 @@
       <c r="D22" s="10"/>
     </row>
     <row r="23" ht="17" spans="1:4">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="15" t="s">
         <v>73</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -3032,7 +3094,7 @@
       <c r="D23" s="10"/>
     </row>
     <row r="24" ht="17" spans="1:4">
-      <c r="A24" s="8"/>
+      <c r="A24" s="15"/>
       <c r="B24" s="4" t="s">
         <v>66</v>
       </c>
@@ -3042,7 +3104,7 @@
       <c r="D24" s="10"/>
     </row>
     <row r="25" ht="17" spans="1:4">
-      <c r="A25" s="8"/>
+      <c r="A25" s="15"/>
       <c r="B25" s="4" t="s">
         <v>67</v>
       </c>
@@ -3052,7 +3114,7 @@
       <c r="D25" s="10"/>
     </row>
     <row r="26" ht="17" spans="1:4">
-      <c r="A26" s="8"/>
+      <c r="A26" s="15"/>
       <c r="B26" s="4" t="s">
         <v>68</v>
       </c>
@@ -3062,7 +3124,7 @@
       <c r="D26" s="10"/>
     </row>
     <row r="27" ht="17" spans="1:4">
-      <c r="A27" s="8"/>
+      <c r="A27" s="15"/>
       <c r="B27" s="4" t="s">
         <v>69</v>
       </c>
@@ -3072,7 +3134,7 @@
       <c r="D27" s="10"/>
     </row>
     <row r="28" ht="17" spans="1:4">
-      <c r="A28" s="8"/>
+      <c r="A28" s="15"/>
       <c r="B28" s="4" t="s">
         <v>70</v>
       </c>
@@ -3149,7 +3211,7 @@
       </c>
     </row>
     <row r="5" ht="17" spans="1:4">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="15" t="s">
         <v>64</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -3161,7 +3223,7 @@
       <c r="D5" s="10"/>
     </row>
     <row r="6" ht="17" spans="1:4">
-      <c r="A6" s="8"/>
+      <c r="A6" s="15"/>
       <c r="B6" s="4" t="s">
         <v>66</v>
       </c>
@@ -3171,7 +3233,7 @@
       <c r="D6" s="10"/>
     </row>
     <row r="7" ht="17" spans="1:4">
-      <c r="A7" s="8"/>
+      <c r="A7" s="15"/>
       <c r="B7" s="4" t="s">
         <v>67</v>
       </c>
@@ -3181,7 +3243,7 @@
       <c r="D7" s="10"/>
     </row>
     <row r="8" ht="17" spans="1:4">
-      <c r="A8" s="8"/>
+      <c r="A8" s="15"/>
       <c r="B8" s="4" t="s">
         <v>68</v>
       </c>
@@ -3191,7 +3253,7 @@
       <c r="D8" s="10"/>
     </row>
     <row r="9" ht="17" spans="1:4">
-      <c r="A9" s="8"/>
+      <c r="A9" s="15"/>
       <c r="B9" s="4" t="s">
         <v>69</v>
       </c>
@@ -3201,7 +3263,7 @@
       <c r="D9" s="10"/>
     </row>
     <row r="10" ht="17" spans="1:4">
-      <c r="A10" s="8"/>
+      <c r="A10" s="15"/>
       <c r="B10" s="4" t="s">
         <v>70</v>
       </c>
@@ -3211,19 +3273,19 @@
       <c r="D10" s="10"/>
     </row>
     <row r="11" ht="17" spans="1:4">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="15" t="s">
         <v>71</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="10"/>
     </row>
     <row r="12" ht="17" spans="1:4">
-      <c r="A12" s="8"/>
+      <c r="A12" s="15"/>
       <c r="B12" s="4" t="s">
         <v>66</v>
       </c>
@@ -3233,7 +3295,7 @@
       <c r="D12" s="10"/>
     </row>
     <row r="13" ht="17" spans="1:4">
-      <c r="A13" s="8"/>
+      <c r="A13" s="15"/>
       <c r="B13" s="4" t="s">
         <v>67</v>
       </c>
@@ -3243,7 +3305,7 @@
       <c r="D13" s="10"/>
     </row>
     <row r="14" ht="17" spans="1:4">
-      <c r="A14" s="8"/>
+      <c r="A14" s="15"/>
       <c r="B14" s="4" t="s">
         <v>68</v>
       </c>
@@ -3253,7 +3315,7 @@
       <c r="D14" s="10"/>
     </row>
     <row r="15" ht="17" spans="1:4">
-      <c r="A15" s="8"/>
+      <c r="A15" s="15"/>
       <c r="B15" s="4" t="s">
         <v>70</v>
       </c>
@@ -3263,7 +3325,7 @@
       <c r="D15" s="10"/>
     </row>
     <row r="16" ht="17" spans="1:4">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="15" t="s">
         <v>72</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -3275,7 +3337,7 @@
       <c r="D16" s="10"/>
     </row>
     <row r="17" ht="17" spans="1:4">
-      <c r="A17" s="8"/>
+      <c r="A17" s="15"/>
       <c r="B17" s="4" t="s">
         <v>66</v>
       </c>
@@ -3285,7 +3347,7 @@
       <c r="D17" s="10"/>
     </row>
     <row r="18" ht="17" spans="1:4">
-      <c r="A18" s="8"/>
+      <c r="A18" s="15"/>
       <c r="B18" s="4" t="s">
         <v>67</v>
       </c>
@@ -3295,7 +3357,7 @@
       <c r="D18" s="10"/>
     </row>
     <row r="19" ht="17" spans="1:4">
-      <c r="A19" s="8"/>
+      <c r="A19" s="15"/>
       <c r="B19" s="4" t="s">
         <v>68</v>
       </c>
@@ -3305,7 +3367,7 @@
       <c r="D19" s="10"/>
     </row>
     <row r="20" ht="17" spans="1:4">
-      <c r="A20" s="8"/>
+      <c r="A20" s="15"/>
       <c r="B20" s="4" t="s">
         <v>70</v>
       </c>
@@ -3315,7 +3377,7 @@
       <c r="D20" s="10"/>
     </row>
     <row r="21" ht="17" spans="1:4">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="15" t="s">
         <v>73</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -3327,7 +3389,7 @@
       <c r="D21" s="10"/>
     </row>
     <row r="22" ht="17" spans="1:4">
-      <c r="A22" s="8"/>
+      <c r="A22" s="15"/>
       <c r="B22" s="4" t="s">
         <v>66</v>
       </c>
@@ -3337,7 +3399,7 @@
       <c r="D22" s="10"/>
     </row>
     <row r="23" ht="17" spans="1:4">
-      <c r="A23" s="8"/>
+      <c r="A23" s="15"/>
       <c r="B23" s="4" t="s">
         <v>67</v>
       </c>
@@ -3347,7 +3409,7 @@
       <c r="D23" s="10"/>
     </row>
     <row r="24" ht="17" spans="1:4">
-      <c r="A24" s="8"/>
+      <c r="A24" s="15"/>
       <c r="B24" s="4" t="s">
         <v>68</v>
       </c>
@@ -3357,7 +3419,7 @@
       <c r="D24" s="10"/>
     </row>
     <row r="25" ht="17" spans="1:4">
-      <c r="A25" s="8"/>
+      <c r="A25" s="15"/>
       <c r="B25" s="4" t="s">
         <v>70</v>
       </c>
@@ -3462,7 +3524,7 @@
       </c>
     </row>
     <row r="7" ht="17" spans="1:4">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="15" t="s">
         <v>64</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -3474,7 +3536,7 @@
       <c r="D7" s="10"/>
     </row>
     <row r="8" ht="17" spans="1:4">
-      <c r="A8" s="8"/>
+      <c r="A8" s="15"/>
       <c r="B8" s="4" t="s">
         <v>80</v>
       </c>
@@ -3484,7 +3546,7 @@
       <c r="D8" s="10"/>
     </row>
     <row r="9" ht="17" spans="1:4">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="15" t="s">
         <v>71</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -3496,7 +3558,7 @@
       <c r="D9" s="10"/>
     </row>
     <row r="10" ht="17" spans="1:4">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="15" t="s">
         <v>72</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -3508,7 +3570,7 @@
       <c r="D10" s="10"/>
     </row>
     <row r="11" ht="17" spans="1:4">
-      <c r="A11" s="8"/>
+      <c r="A11" s="15"/>
       <c r="B11" s="4" t="s">
         <v>83</v>
       </c>
@@ -3518,7 +3580,7 @@
       <c r="D11" s="10"/>
     </row>
     <row r="12" ht="17" spans="1:4">
-      <c r="A12" s="8"/>
+      <c r="A12" s="15"/>
       <c r="B12" s="4" t="s">
         <v>84</v>
       </c>
@@ -3528,7 +3590,7 @@
       <c r="D12" s="10"/>
     </row>
     <row r="13" ht="84" spans="1:4">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="15" t="s">
         <v>73</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -3542,7 +3604,7 @@
       </c>
     </row>
     <row r="14" ht="84" spans="1:4">
-      <c r="A14" s="8"/>
+      <c r="A14" s="15"/>
       <c r="B14" s="4" t="s">
         <v>47</v>
       </c>
@@ -3554,7 +3616,7 @@
       </c>
     </row>
     <row r="15" ht="84" spans="1:4">
-      <c r="A15" s="8"/>
+      <c r="A15" s="15"/>
       <c r="B15" s="4" t="s">
         <v>48</v>
       </c>
@@ -3566,8 +3628,8 @@
       </c>
     </row>
     <row r="16" ht="17" spans="1:4">
-      <c r="A16" s="8"/>
-      <c r="B16" s="14" t="s">
+      <c r="A16" s="15"/>
+      <c r="B16" s="17" t="s">
         <v>88</v>
       </c>
       <c r="C16" s="9" t="s">
@@ -3576,8 +3638,8 @@
       <c r="D16" s="10"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="8"/>
-      <c r="B17" s="15" t="s">
+      <c r="A17" s="15"/>
+      <c r="B17" s="18" t="s">
         <v>89</v>
       </c>
       <c r="C17" s="9" t="s">
@@ -3586,46 +3648,46 @@
       <c r="D17" s="10"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="18" t="s">
         <v>91</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="13"/>
+      <c r="D18" s="14"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="8"/>
-      <c r="B19" s="13" t="s">
+      <c r="A19" s="15"/>
+      <c r="B19" s="14" t="s">
         <v>92</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="13"/>
+      <c r="D19" s="14"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="8"/>
-      <c r="B20" s="15" t="s">
+      <c r="A20" s="15"/>
+      <c r="B20" s="18" t="s">
         <v>93</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="13"/>
+      <c r="D20" s="14"/>
     </row>
     <row r="21" ht="17" spans="1:4">
-      <c r="A21" s="8"/>
+      <c r="A21" s="15"/>
       <c r="B21" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="13"/>
+      <c r="D21" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3704,7 +3766,7 @@
       </c>
     </row>
     <row r="5" ht="17" spans="1:4">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="15" t="s">
         <v>72</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -3718,7 +3780,7 @@
       </c>
     </row>
     <row r="6" ht="17" spans="1:4">
-      <c r="A6" s="8"/>
+      <c r="A6" s="15"/>
       <c r="B6" s="4" t="s">
         <v>98</v>
       </c>
@@ -3730,11 +3792,11 @@
       </c>
     </row>
     <row r="7" ht="17" spans="1:4">
-      <c r="A7" s="8"/>
+      <c r="A7" s="15"/>
       <c r="B7" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="10" t="s">
@@ -3742,11 +3804,11 @@
       </c>
     </row>
     <row r="8" ht="17" spans="1:4">
-      <c r="A8" s="8"/>
+      <c r="A8" s="15"/>
       <c r="B8" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="10" t="s">
@@ -3754,11 +3816,11 @@
       </c>
     </row>
     <row r="9" ht="17" spans="1:4">
-      <c r="A9" s="8"/>
+      <c r="A9" s="15"/>
       <c r="B9" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -3766,7 +3828,7 @@
       </c>
     </row>
     <row r="10" ht="17" spans="1:4">
-      <c r="A10" s="8"/>
+      <c r="A10" s="15"/>
       <c r="B10" s="4" t="s">
         <v>102</v>
       </c>
@@ -3776,37 +3838,37 @@
       <c r="D10" s="10"/>
     </row>
     <row r="11" ht="17" spans="1:4">
-      <c r="A11" s="8"/>
+      <c r="A11" s="15"/>
       <c r="B11" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="10"/>
     </row>
     <row r="12" ht="17" spans="1:4">
-      <c r="A12" s="8"/>
+      <c r="A12" s="15"/>
       <c r="B12" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="10"/>
     </row>
     <row r="13" ht="17" spans="1:4">
-      <c r="A13" s="8"/>
+      <c r="A13" s="15"/>
       <c r="B13" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D13" s="10"/>
     </row>
     <row r="14" ht="17" spans="1:4">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="15" t="s">
         <v>73</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -3818,7 +3880,7 @@
       <c r="D14" s="4"/>
     </row>
     <row r="15" ht="17" spans="1:4">
-      <c r="A15" s="8"/>
+      <c r="A15" s="15"/>
       <c r="B15" s="4" t="s">
         <v>98</v>
       </c>
@@ -3828,30 +3890,30 @@
       <c r="D15" s="4"/>
     </row>
     <row r="16" ht="17" spans="1:4">
-      <c r="A16" s="8"/>
+      <c r="A16" s="15"/>
       <c r="B16" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>30</v>
+      <c r="C16" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D16" s="4"/>
     </row>
     <row r="17" ht="18" spans="1:4">
-      <c r="A17" s="8"/>
-      <c r="B17" s="12" t="s">
+      <c r="A17" s="15"/>
+      <c r="B17" s="13" t="s">
         <v>107</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="13" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:4">
-      <c r="A18" s="8"/>
-      <c r="B18" s="12" t="s">
+      <c r="A18" s="15"/>
+      <c r="B18" s="13" t="s">
         <v>109</v>
       </c>
       <c r="C18" s="9" t="s">
@@ -3860,54 +3922,54 @@
       <c r="D18" s="10"/>
     </row>
     <row r="19" ht="18" spans="1:4">
-      <c r="A19" s="8"/>
-      <c r="B19" s="12" t="s">
+      <c r="A19" s="15"/>
+      <c r="B19" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="13"/>
+      <c r="C19" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="14"/>
     </row>
     <row r="20" ht="18" spans="1:4">
-      <c r="A20" s="8"/>
-      <c r="B20" s="12" t="s">
+      <c r="A20" s="15"/>
+      <c r="B20" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="13"/>
+      <c r="C20" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="14"/>
     </row>
     <row r="21" ht="18" spans="1:4">
-      <c r="A21" s="8"/>
-      <c r="B21" s="12" t="s">
+      <c r="A21" s="15"/>
+      <c r="B21" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="13"/>
+      <c r="C21" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="14"/>
     </row>
     <row r="22" ht="17" spans="1:4">
-      <c r="A22" s="8"/>
+      <c r="A22" s="15"/>
       <c r="B22" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="13"/>
+      <c r="C22" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="14"/>
     </row>
     <row r="23" ht="17" spans="1:4">
-      <c r="A23" s="8"/>
+      <c r="A23" s="15"/>
       <c r="B23" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="13"/>
+      <c r="C23" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3917,7 +3979,314 @@
     <mergeCell ref="A14:A23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14 C15 C16 C17 C18 C2:C3 C5:C13 C19:C23">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C16 C19 C20 C21 C22 C23 C2:C3 C5:C15 C17:C18">
+      <formula1>"未进行,进行中,已暂停,已完成"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D30"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="3"/>
+  <cols>
+    <col min="2" max="2" width="64.0961538461538" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.9038461538462" style="1" customWidth="1"/>
+    <col min="4" max="4" width="47.75" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customHeight="1" spans="1:4">
+      <c r="A1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" ht="18.65" customHeight="1" spans="1:4">
+      <c r="A2" s="2"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" ht="21.6" customHeight="1" spans="1:4">
+      <c r="A3" s="2"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" ht="17" spans="1:4">
+      <c r="A5" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="10"/>
+    </row>
+    <row r="6" ht="17" spans="1:4">
+      <c r="A6" s="11"/>
+      <c r="B6" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="10"/>
+    </row>
+    <row r="7" ht="17" spans="1:4">
+      <c r="A7" s="11"/>
+      <c r="B7" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="10"/>
+    </row>
+    <row r="8" ht="17" spans="1:4">
+      <c r="A8" s="11"/>
+      <c r="B8" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="10"/>
+    </row>
+    <row r="9" ht="17" spans="1:4">
+      <c r="A9" s="11"/>
+      <c r="B9" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="10"/>
+    </row>
+    <row r="10" ht="17" spans="1:4">
+      <c r="A10" s="11"/>
+      <c r="B10" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="10"/>
+    </row>
+    <row r="11" ht="17" spans="1:4">
+      <c r="A11" s="11"/>
+      <c r="B11" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="10"/>
+    </row>
+    <row r="12" ht="17" spans="1:4">
+      <c r="A12" s="11"/>
+      <c r="B12" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="10"/>
+    </row>
+    <row r="13" ht="17" spans="1:4">
+      <c r="A13" s="11"/>
+      <c r="B13" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="10"/>
+    </row>
+    <row r="14" ht="17" spans="1:4">
+      <c r="A14" s="11"/>
+      <c r="B14" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="10"/>
+    </row>
+    <row r="15" ht="17" spans="1:4">
+      <c r="A15" s="11"/>
+      <c r="B15" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="10"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="10"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="11"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="10"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="11"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="10"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="12"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="10"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="10"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="11"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="11"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="11"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" ht="17.6" spans="1:4">
+      <c r="A24" s="11"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="13"/>
+    </row>
+    <row r="25" ht="17.6" spans="1:4">
+      <c r="A25" s="12"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" s="10"/>
+    </row>
+    <row r="26" ht="17.6" spans="1:4">
+      <c r="A26" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="14"/>
+    </row>
+    <row r="27" ht="17.6" spans="1:4">
+      <c r="A27" s="11"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="14"/>
+    </row>
+    <row r="28" ht="17.6" spans="1:4">
+      <c r="A28" s="11"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="14"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="11"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="14"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="12"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="A5:A15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A20:A25"/>
+    <mergeCell ref="A26:A30"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5 C6 C15 C2:C3 C7:C8 C9:C14 C16:C30">
       <formula1>"未进行,进行中,已暂停,已完成"</formula1>
     </dataValidation>
   </dataValidations>

--- a/file/personal/roleImportant/角色要事记录表_2026.xlsx
+++ b/file/personal/roleImportant/角色要事记录表_2026.xlsx
@@ -465,6 +465,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
       <t>周三:数量5图形5推理</t>
     </r>
     <r>
@@ -3979,7 +3985,7 @@
     <mergeCell ref="A14:A23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C16 C19 C20 C21 C22 C23 C2:C3 C5:C15 C17:C18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C3 C5:C23">
       <formula1>"未进行,进行中,已暂停,已完成"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4115,8 +4121,8 @@
       <c r="B12" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>30</v>
+      <c r="C12" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D12" s="10"/>
     </row>
@@ -4286,7 +4292,7 @@
     <mergeCell ref="A26:A30"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5 C6 C15 C2:C3 C7:C8 C9:C14 C16:C30">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12 C2:C3 C5:C11 C13:C30">
       <formula1>"未进行,进行中,已暂停,已完成"</formula1>
     </dataValidation>
   </dataValidations>

--- a/file/personal/roleImportant/角色要事记录表_2026.xlsx
+++ b/file/personal/roleImportant/角色要事记录表_2026.xlsx
@@ -4061,8 +4061,8 @@
       <c r="B6" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>30</v>
+      <c r="C6" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D6" s="10"/>
     </row>
@@ -4071,8 +4071,8 @@
       <c r="B7" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>30</v>
+      <c r="C7" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D7" s="10"/>
     </row>
@@ -4131,8 +4131,8 @@
       <c r="B13" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>30</v>
+      <c r="C13" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D13" s="10"/>
     </row>
@@ -4292,7 +4292,7 @@
     <mergeCell ref="A26:A30"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12 C2:C3 C5:C11 C13:C30">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7 C2:C3 C5:C6 C8:C30">
       <formula1>"未进行,进行中,已暂停,已完成"</formula1>
     </dataValidation>
   </dataValidations>

--- a/file/personal/roleImportant/角色要事记录表_2026.xlsx
+++ b/file/personal/roleImportant/角色要事记录表_2026.xlsx
@@ -4101,8 +4101,8 @@
       <c r="B10" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>30</v>
+      <c r="C10" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D10" s="10"/>
     </row>
@@ -4292,7 +4292,7 @@
     <mergeCell ref="A26:A30"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7 C2:C3 C5:C6 C8:C30">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C10 C2:C3 C5:C9 C11:C30">
       <formula1>"未进行,进行中,已暂停,已完成"</formula1>
     </dataValidation>
   </dataValidations>

--- a/file/personal/roleImportant/角色要事记录表_2026.xlsx
+++ b/file/personal/roleImportant/角色要事记录表_2026.xlsx
@@ -4141,8 +4141,8 @@
       <c r="B14" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>30</v>
+      <c r="C14" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D14" s="10"/>
     </row>
@@ -4292,7 +4292,7 @@
     <mergeCell ref="A26:A30"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C10 C2:C3 C5:C9 C11:C30">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14 C2:C3 C5:C13 C15:C30">
       <formula1>"未进行,进行中,已暂停,已完成"</formula1>
     </dataValidation>
   </dataValidations>

--- a/file/personal/roleImportant/角色要事记录表_2026.xlsx
+++ b/file/personal/roleImportant/角色要事记录表_2026.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="122">
   <si>
     <t>角色</t>
   </si>
@@ -723,6 +723,9 @@
   </si>
   <si>
     <t>专业知识预测考题读：3遍</t>
+  </si>
+  <si>
+    <t>专业知识预测考题读：4遍</t>
   </si>
 </sst>
 </file>
@@ -3998,7 +4001,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="64.0961538461538" style="1" customWidth="1"/>
@@ -4032,34 +4035,32 @@
       </c>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="6" t="s">
+    <row r="4" ht="21.6" customHeight="1" spans="1:4">
+      <c r="A4" s="2"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="6" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="5" ht="17" spans="1:4">
-      <c r="A5" s="8" t="s">
+    <row r="6" ht="17" spans="1:4">
+      <c r="A6" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B6" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="10"/>
-    </row>
-    <row r="6" ht="17" spans="1:4">
-      <c r="A6" s="11"/>
-      <c r="B6" s="4" t="s">
-        <v>115</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>35</v>
@@ -4069,7 +4070,7 @@
     <row r="7" ht="17" spans="1:4">
       <c r="A7" s="11"/>
       <c r="B7" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>35</v>
@@ -4079,27 +4080,27 @@
     <row r="8" ht="17" spans="1:4">
       <c r="A8" s="11"/>
       <c r="B8" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>30</v>
+        <v>116</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D8" s="10"/>
     </row>
     <row r="9" ht="17" spans="1:4">
       <c r="A9" s="11"/>
       <c r="B9" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>30</v>
+        <v>117</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D9" s="10"/>
     </row>
     <row r="10" ht="17" spans="1:4">
       <c r="A10" s="11"/>
       <c r="B10" s="4" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>35</v>
@@ -4109,10 +4110,10 @@
     <row r="11" ht="17" spans="1:4">
       <c r="A11" s="11"/>
       <c r="B11" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>30</v>
+        <v>96</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="D11" s="10"/>
     </row>
@@ -4149,25 +4150,27 @@
     <row r="15" ht="17" spans="1:4">
       <c r="A15" s="11"/>
       <c r="B15" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="10"/>
+    </row>
+    <row r="16" ht="17" spans="1:4">
+      <c r="A16" s="11"/>
+      <c r="B16" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="10"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="8" t="s">
+      <c r="C16" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="10"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="10"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="11"/>
       <c r="B17" s="4"/>
       <c r="C17" s="5" t="s">
         <v>30</v>
@@ -4183,7 +4186,7 @@
       <c r="D18" s="10"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="12"/>
+      <c r="A19" s="11"/>
       <c r="B19" s="4"/>
       <c r="C19" s="5" t="s">
         <v>30</v>
@@ -4191,9 +4194,7 @@
       <c r="D19" s="10"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="8" t="s">
-        <v>72</v>
-      </c>
+      <c r="A20" s="11"/>
       <c r="B20" s="4"/>
       <c r="C20" s="5" t="s">
         <v>30</v>
@@ -4201,20 +4202,22 @@
       <c r="D20" s="10"/>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="11"/>
+      <c r="A21" s="12"/>
       <c r="B21" s="4"/>
       <c r="C21" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="10"/>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="11"/>
+      <c r="A22" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="B22" s="4"/>
       <c r="C22" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="4"/>
+      <c r="D22" s="10"/>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="11"/>
@@ -4224,75 +4227,91 @@
       </c>
       <c r="D23" s="4"/>
     </row>
-    <row r="24" ht="17.6" spans="1:4">
+    <row r="24" spans="1:4">
       <c r="A24" s="11"/>
-      <c r="B24" s="13"/>
+      <c r="B24" s="4"/>
       <c r="C24" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="13"/>
-    </row>
-    <row r="25" ht="17.6" spans="1:4">
-      <c r="A25" s="12"/>
-      <c r="B25" s="13"/>
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="11"/>
+      <c r="B25" s="4"/>
       <c r="C25" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D25" s="10"/>
+      <c r="D25" s="4"/>
     </row>
     <row r="26" ht="17.6" spans="1:4">
-      <c r="A26" s="8" t="s">
-        <v>73</v>
-      </c>
+      <c r="A26" s="11"/>
       <c r="B26" s="13"/>
       <c r="C26" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D26" s="14"/>
+      <c r="D26" s="13"/>
     </row>
     <row r="27" ht="17.6" spans="1:4">
-      <c r="A27" s="11"/>
+      <c r="A27" s="12"/>
       <c r="B27" s="13"/>
       <c r="C27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="14"/>
+      <c r="D27" s="10"/>
     </row>
     <row r="28" ht="17.6" spans="1:4">
-      <c r="A28" s="11"/>
+      <c r="A28" s="8" t="s">
+        <v>73</v>
+      </c>
       <c r="B28" s="13"/>
       <c r="C28" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D28" s="14"/>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" ht="17.6" spans="1:4">
       <c r="A29" s="11"/>
-      <c r="B29" s="4"/>
+      <c r="B29" s="13"/>
       <c r="C29" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D29" s="14"/>
     </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="12"/>
-      <c r="B30" s="4"/>
+    <row r="30" ht="17.6" spans="1:4">
+      <c r="A30" s="11"/>
+      <c r="B30" s="13"/>
       <c r="C30" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D30" s="14"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="11"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="14"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="12"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="A5:A15"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="A20:A25"/>
-    <mergeCell ref="A26:A30"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="A6:A16"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A28:A32"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14 C2:C3 C5:C13 C15:C30">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2 C3 C4 C9 C10 C11 C15 C16 C19 C6:C8 C12:C14 C17:C18 C20:C32">
       <formula1>"未进行,进行中,已暂停,已完成"</formula1>
     </dataValidation>
   </dataValidations>

--- a/file/personal/roleImportant/角色要事记录表_2026.xlsx
+++ b/file/personal/roleImportant/角色要事记录表_2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22980" windowHeight="13160" tabRatio="500" activeTab="6"/>
+    <workbookView windowWidth="22980" windowHeight="13160" tabRatio="500" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="角色目录" sheetId="1" r:id="rId1"/>
@@ -14,9 +14,10 @@
     <sheet name="四月" sheetId="5" r:id="rId5"/>
     <sheet name="五月" sheetId="6" r:id="rId6"/>
     <sheet name="六月" sheetId="7" r:id="rId7"/>
+    <sheet name="七月" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">待办任务!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">待办任务!$A$1:$D$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="147">
   <si>
     <t>角色</t>
   </si>
@@ -171,6 +172,9 @@
   </si>
   <si>
     <t>考虑下提升学历</t>
+  </si>
+  <si>
+    <t>考社工证</t>
   </si>
   <si>
     <t>关注下半年其它单位自主招生情况</t>
@@ -716,6 +720,12 @@
     <t>专业知识预测考题写：1遍</t>
   </si>
   <si>
+    <t>十二点睡觉-七点起床</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
     <t>周一:数量5图形5推理5言语10常识2</t>
   </si>
   <si>
@@ -757,6 +767,42 @@
   </si>
   <si>
     <t>时间来不及,现在最缺的就是时间,现在考很不划算,考出非全日制的作用也不大</t>
+  </si>
+  <si>
+    <t>周三</t>
+  </si>
+  <si>
+    <t>视频4、11-12看书</t>
+  </si>
+  <si>
+    <t>周四</t>
+  </si>
+  <si>
+    <t>7-8看书、视频4、11-12看书</t>
+  </si>
+  <si>
+    <t>周五</t>
+  </si>
+  <si>
+    <t>周六</t>
+  </si>
+  <si>
+    <t>视频4、图书馆8-5、10-12看书</t>
+  </si>
+  <si>
+    <t>周日</t>
+  </si>
+  <si>
+    <t>周一</t>
+  </si>
+  <si>
+    <t>周二</t>
+  </si>
+  <si>
+    <t>视频4、考试、10-12看书</t>
+  </si>
+  <si>
+    <t>做计划</t>
   </si>
 </sst>
 </file>
@@ -1222,7 +1268,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1249,12 +1295,60 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -1402,7 +1496,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1414,34 +1508,34 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1526,7 +1620,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1536,29 +1630,50 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1569,6 +1684,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
@@ -1635,19 +1759,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2257,231 +2381,231 @@
   <dimension ref="A1:E30"/>
   <sheetFormatPr defaultColWidth="6" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="14.4134615384615" style="17" customWidth="1"/>
-    <col min="2" max="16384" width="6" style="17"/>
+    <col min="1" max="1" width="14.4134615384615" style="27" customWidth="1"/>
+    <col min="2" max="16384" width="6" style="27"/>
   </cols>
   <sheetData>
     <row r="1" ht="14" customHeight="1" spans="1:5">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
     </row>
     <row r="2" ht="14" customHeight="1" spans="1:5">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
     </row>
     <row r="3" ht="14" customHeight="1" spans="1:5">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
     </row>
     <row r="4" ht="14" customHeight="1" spans="1:5">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
     </row>
     <row r="5" ht="14" customHeight="1" spans="1:5">
-      <c r="A5" s="40"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
+      <c r="A5" s="50"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
     </row>
     <row r="6" ht="14" customHeight="1" spans="1:5">
-      <c r="A6" s="40"/>
-      <c r="B6" s="37"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
+      <c r="A6" s="50"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
     </row>
     <row r="7" ht="14" customHeight="1" spans="1:5">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
     </row>
     <row r="8" ht="14" customHeight="1" spans="1:5">
-      <c r="A8" s="40"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
+      <c r="A8" s="50"/>
+      <c r="B8" s="47"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
     </row>
     <row r="9" ht="14" customHeight="1" spans="1:5">
-      <c r="A9" s="40"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
+      <c r="A9" s="50"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
     </row>
     <row r="10" ht="14" customHeight="1" spans="1:5">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="37"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
     </row>
     <row r="11" ht="14" customHeight="1" spans="1:5">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
+      <c r="B11" s="47"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
     </row>
     <row r="12" ht="14" customHeight="1" spans="1:5">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="37"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
     </row>
     <row r="13" ht="14" customHeight="1" spans="1:5">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="37"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
     </row>
     <row r="14" ht="14" customHeight="1" spans="1:5">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="37"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
     </row>
     <row r="15" ht="14" customHeight="1" spans="1:5">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="37"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
     </row>
     <row r="16" ht="14" customHeight="1" spans="1:5">
-      <c r="A16" s="40" t="s">
+      <c r="A16" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="37"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
     </row>
     <row r="17" ht="14" customHeight="1" spans="1:5">
-      <c r="A17" s="40" t="s">
+      <c r="A17" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="37"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
+      <c r="B17" s="47"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
     </row>
     <row r="18" ht="14" customHeight="1" spans="1:5">
-      <c r="A18" s="40" t="s">
+      <c r="A18" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="37"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
+      <c r="B18" s="47"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
     </row>
     <row r="19" ht="14" customHeight="1" spans="1:5">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="37"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
     </row>
     <row r="20" ht="14" customHeight="1" spans="1:5">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="37"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
+      <c r="B20" s="47"/>
+      <c r="C20" s="48"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
     </row>
     <row r="21" ht="14" customHeight="1" spans="1:5">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="37"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
     </row>
     <row r="22" ht="14" customHeight="1" spans="1:5">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="37"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
     </row>
     <row r="23" ht="14" customHeight="1" spans="1:5">
-      <c r="A23" s="39" t="s">
+      <c r="A23" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
+      <c r="B23" s="47"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="48"/>
     </row>
     <row r="26" ht="13.5" customHeight="1" spans="1:5">
-      <c r="A26" s="41" t="s">
+      <c r="A26" s="51" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="27" ht="13.5" customHeight="1" spans="1:5">
-      <c r="A27" s="24" t="s">
+      <c r="A27" s="34" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="28" ht="13.5" customHeight="1" spans="1:5">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="40" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="29" ht="13.5" customHeight="1" spans="1:5">
-      <c r="A29" s="27" t="s">
+      <c r="A29" s="37" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="30" ht="13.5" customHeight="1" spans="1:5">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="24" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2503,404 +2627,417 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="16.3557692307692" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="16.3557692307692" style="17"/>
-    <col min="2" max="2" width="99.1153846153846" style="18" customWidth="1"/>
-    <col min="3" max="3" width="14.0961538461538" style="18" customWidth="1"/>
-    <col min="4" max="4" width="16.3557692307692" style="17"/>
-    <col min="5" max="5" width="18.2692307692308" style="17" customWidth="1"/>
-    <col min="6" max="6" width="17.7788461538462" style="17" customWidth="1"/>
-    <col min="7" max="16384" width="16.3557692307692" style="17"/>
+    <col min="1" max="1" width="16.3557692307692" style="27"/>
+    <col min="2" max="2" width="99.1153846153846" style="28" customWidth="1"/>
+    <col min="3" max="3" width="14.0961538461538" style="28" customWidth="1"/>
+    <col min="4" max="4" width="16.3557692307692" style="27"/>
+    <col min="5" max="5" width="18.2692307692308" style="27" customWidth="1"/>
+    <col min="6" max="6" width="17.7788461538462" style="27" customWidth="1"/>
+    <col min="7" max="16384" width="16.3557692307692" style="27"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.55" customHeight="1" spans="1:5">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="10"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="2" ht="13.35" customHeight="1" spans="1:5">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="10"/>
+      <c r="D2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="16"/>
     </row>
     <row r="3" ht="13.35" customHeight="1" spans="1:5">
-      <c r="A3" s="22"/>
-      <c r="B3" s="23" t="s">
+      <c r="A3" s="32"/>
+      <c r="B3" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="10"/>
+      <c r="D3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="16"/>
     </row>
     <row r="4" ht="13.35" customHeight="1" spans="1:5">
-      <c r="A4" s="22"/>
-      <c r="B4" s="25" t="s">
+      <c r="A4" s="32"/>
+      <c r="B4" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="10"/>
+      <c r="D4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="16"/>
     </row>
     <row r="5" ht="13" customHeight="1" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="10"/>
+      <c r="D5" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="16"/>
     </row>
     <row r="6" ht="13" customHeight="1" spans="1:5">
       <c r="A6" s="2"/>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="10"/>
+      <c r="D6" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="16"/>
     </row>
     <row r="7" ht="13" customHeight="1" spans="1:5">
       <c r="A7" s="2"/>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="10"/>
+      <c r="D7" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="16"/>
     </row>
     <row r="8" ht="13" customHeight="1" spans="1:5">
       <c r="A8" s="2"/>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="10"/>
+      <c r="D8" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="16"/>
     </row>
     <row r="9" ht="13" customHeight="1" spans="1:5">
       <c r="A9" s="2"/>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="10"/>
+      <c r="D9" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="16"/>
     </row>
     <row r="10" ht="13" customHeight="1" spans="1:5">
       <c r="A10" s="2"/>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="10"/>
+      <c r="D10" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="16"/>
     </row>
     <row r="11" ht="13" customHeight="1" spans="1:5">
       <c r="A11" s="2"/>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="10"/>
+      <c r="D11" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="16"/>
     </row>
     <row r="12" ht="13" customHeight="1" spans="1:5">
       <c r="A12" s="2"/>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="10"/>
+      <c r="D12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="16"/>
     </row>
     <row r="13" ht="13" customHeight="1" spans="1:5">
       <c r="A13" s="2"/>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="10"/>
+      <c r="D13" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="16"/>
     </row>
     <row r="14" ht="13" customHeight="1" spans="1:5">
       <c r="A14" s="2"/>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="10"/>
+      <c r="D14" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="16"/>
     </row>
     <row r="15" ht="13" customHeight="1" spans="1:5">
       <c r="A15" s="2"/>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" s="10"/>
-    </row>
-    <row r="16" ht="23.1" customHeight="1" spans="1:5">
-      <c r="A16" s="2" t="s">
+      <c r="D15" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="16"/>
+    </row>
+    <row r="16" ht="13" customHeight="1" spans="1:5">
+      <c r="A16" s="2"/>
+      <c r="B16" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="C16" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="16"/>
+    </row>
+    <row r="17" ht="23.1" customHeight="1" spans="1:5">
+      <c r="A17" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="B17" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="10"/>
-    </row>
-    <row r="17" ht="17.9" customHeight="1" spans="1:5">
-      <c r="A17" s="2"/>
-      <c r="B17" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="30" t="s">
+      <c r="D17" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="16"/>
+    </row>
+    <row r="18" ht="17.9" customHeight="1" spans="1:5">
+      <c r="A18" s="2"/>
+      <c r="B18" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" s="10"/>
-    </row>
-    <row r="18" ht="20.1" customHeight="1" spans="1:5">
-      <c r="A18" s="2"/>
-      <c r="B18" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="30" t="s">
+      <c r="D18" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="16"/>
+    </row>
+    <row r="19" ht="20.1" customHeight="1" spans="1:5">
+      <c r="A19" s="2"/>
+      <c r="B19" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="10"/>
-    </row>
-    <row r="19" ht="22.35" customHeight="1" spans="1:5">
-      <c r="A19" s="2"/>
-      <c r="B19" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="30" t="s">
+      <c r="D19" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="16"/>
+    </row>
+    <row r="20" ht="22.35" customHeight="1" spans="1:5">
+      <c r="A20" s="2"/>
+      <c r="B20" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="10"/>
-    </row>
-    <row r="20" ht="13" customHeight="1" spans="1:5">
-      <c r="A20" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="4" t="s">
+      <c r="D20" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="16"/>
+    </row>
+    <row r="21" ht="13" customHeight="1" spans="1:5">
+      <c r="A21" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="B21" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="10" t="s">
+      <c r="D21" s="8" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="21" ht="36.55" customHeight="1" spans="1:5">
-      <c r="A21" s="32"/>
-      <c r="B21" s="4" t="s">
+      <c r="E21" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="27" t="s">
+    </row>
+    <row r="22" ht="36.55" customHeight="1" spans="1:5">
+      <c r="A22" s="42"/>
+      <c r="B22" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" s="10"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="32"/>
-      <c r="B22" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="30" t="s">
+      <c r="D22" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="16"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="42"/>
+      <c r="B23" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="10"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="32"/>
-      <c r="B23" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="27" t="s">
+      <c r="D23" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="16"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="42"/>
+      <c r="B24" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="10"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="32"/>
-      <c r="B24" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="27" t="s">
+      <c r="D24" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="16"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="42"/>
+      <c r="B25" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E24" s="10"/>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="32"/>
-      <c r="B25" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C25" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E25" s="10"/>
+      <c r="D25" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="16"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="32"/>
+      <c r="A26" s="42"/>
       <c r="B26" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="C26" s="27" t="s">
+      <c r="C26" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26" s="10"/>
-    </row>
-    <row r="27" ht="17" spans="1:5">
-      <c r="A27" s="33" t="s">
+      <c r="D26" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="16"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="42"/>
+      <c r="B27" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="34" t="s">
+      <c r="C27" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="16"/>
+    </row>
+    <row r="28" ht="17" spans="1:5">
+      <c r="A28" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="27" t="s">
+      <c r="B28" s="44" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E27" s="10"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="B28" s="35"/>
+      <c r="D28" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="16"/>
     </row>
     <row r="29" spans="1:5">
-      <c r="B29" s="35"/>
+      <c r="B29" s="45"/>
     </row>
     <row r="30" spans="1:5">
-      <c r="B30" s="35"/>
+      <c r="B30" s="45"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="B31" s="45"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D27" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D28" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="4">
     <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A5:A15"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="A20:A26"/>
+    <mergeCell ref="A5:A16"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="A21:A27"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D27">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D28">
       <formula1>"未进行,进行中,已暂停,已完成"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2925,285 +3062,285 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="B1" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="6" t="s">
+      <c r="A4" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="11" t="s">
         <v>67</v>
       </c>
+      <c r="D4" s="11" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="5" ht="17" spans="1:4">
-      <c r="A5" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="A5" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="10"/>
+      <c r="B5" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="16"/>
     </row>
     <row r="6" ht="17" spans="1:4">
-      <c r="A6" s="11"/>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="14"/>
+      <c r="B6" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="16"/>
+    </row>
+    <row r="7" ht="17" spans="1:4">
+      <c r="A7" s="14"/>
+      <c r="B7" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="16"/>
+    </row>
+    <row r="8" ht="17" spans="1:4">
+      <c r="A8" s="14"/>
+      <c r="B8" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="16"/>
+    </row>
+    <row r="9" ht="17" spans="1:4">
+      <c r="A9" s="14"/>
+      <c r="B9" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="16"/>
+    </row>
+    <row r="10" ht="17" spans="1:4">
+      <c r="A10" s="14"/>
+      <c r="B10" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="16"/>
+    </row>
+    <row r="11" ht="17" spans="1:4">
+      <c r="A11" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="10"/>
-    </row>
-    <row r="7" ht="17" spans="1:4">
-      <c r="A7" s="11"/>
-      <c r="B7" s="4" t="s">
+      <c r="C11" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="16"/>
+    </row>
+    <row r="12" ht="17" spans="1:4">
+      <c r="A12" s="14"/>
+      <c r="B12" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="10"/>
-    </row>
-    <row r="8" ht="17" spans="1:4">
-      <c r="A8" s="11"/>
-      <c r="B8" s="4" t="s">
+      <c r="C12" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="16"/>
+    </row>
+    <row r="13" ht="17" spans="1:4">
+      <c r="A13" s="14"/>
+      <c r="B13" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="10"/>
-    </row>
-    <row r="9" ht="17" spans="1:4">
-      <c r="A9" s="11"/>
-      <c r="B9" s="4" t="s">
+      <c r="C13" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="16"/>
+    </row>
+    <row r="14" ht="17" spans="1:4">
+      <c r="A14" s="14"/>
+      <c r="B14" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="10"/>
-    </row>
-    <row r="10" ht="17" spans="1:4">
-      <c r="A10" s="11"/>
-      <c r="B10" s="4" t="s">
+      <c r="C14" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="16"/>
+    </row>
+    <row r="15" ht="17" spans="1:4">
+      <c r="A15" s="14"/>
+      <c r="B15" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="10"/>
-    </row>
-    <row r="11" ht="17" spans="1:4">
-      <c r="A11" s="11" t="s">
+      <c r="C15" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="16"/>
+    </row>
+    <row r="16" ht="17" spans="1:4">
+      <c r="A16" s="14"/>
+      <c r="B16" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="10"/>
-    </row>
-    <row r="12" ht="17" spans="1:4">
-      <c r="A12" s="11"/>
-      <c r="B12" s="4" t="s">
+      <c r="C16" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="16"/>
+    </row>
+    <row r="17" ht="17" spans="1:4">
+      <c r="A17" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="10"/>
-    </row>
-    <row r="13" ht="17" spans="1:4">
-      <c r="A13" s="11"/>
-      <c r="B13" s="4" t="s">
+      <c r="C17" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="16"/>
+    </row>
+    <row r="18" ht="17" spans="1:4">
+      <c r="A18" s="14"/>
+      <c r="B18" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="10"/>
-    </row>
-    <row r="14" ht="17" spans="1:4">
-      <c r="A14" s="11"/>
-      <c r="B14" s="4" t="s">
+      <c r="C18" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="16"/>
+    </row>
+    <row r="19" ht="17" spans="1:4">
+      <c r="A19" s="14"/>
+      <c r="B19" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="10"/>
-    </row>
-    <row r="15" ht="17" spans="1:4">
-      <c r="A15" s="11"/>
-      <c r="B15" s="4" t="s">
+      <c r="C19" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="16"/>
+    </row>
+    <row r="20" ht="17" spans="1:4">
+      <c r="A20" s="14"/>
+      <c r="B20" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="10"/>
-    </row>
-    <row r="16" ht="17" spans="1:4">
-      <c r="A16" s="11"/>
-      <c r="B16" s="4" t="s">
+      <c r="C20" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="16"/>
+    </row>
+    <row r="21" ht="17" spans="1:4">
+      <c r="A21" s="14"/>
+      <c r="B21" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="10"/>
-    </row>
-    <row r="17" ht="17" spans="1:4">
-      <c r="A17" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="10"/>
-    </row>
-    <row r="18" ht="17" spans="1:4">
-      <c r="A18" s="11"/>
-      <c r="B18" s="4" t="s">
+      <c r="C21" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="16"/>
+    </row>
+    <row r="22" ht="17" spans="1:4">
+      <c r="A22" s="14"/>
+      <c r="B22" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="16"/>
+    </row>
+    <row r="23" ht="17" spans="1:4">
+      <c r="A23" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="10"/>
-    </row>
-    <row r="19" ht="17" spans="1:4">
-      <c r="A19" s="11"/>
-      <c r="B19" s="4" t="s">
+      <c r="C23" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="16"/>
+    </row>
+    <row r="24" ht="17" spans="1:4">
+      <c r="A24" s="14"/>
+      <c r="B24" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="10"/>
-    </row>
-    <row r="20" ht="17" spans="1:4">
-      <c r="A20" s="11"/>
-      <c r="B20" s="4" t="s">
+      <c r="C24" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="16"/>
+    </row>
+    <row r="25" ht="17" spans="1:4">
+      <c r="A25" s="14"/>
+      <c r="B25" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="10"/>
-    </row>
-    <row r="21" ht="17" spans="1:4">
-      <c r="A21" s="11"/>
-      <c r="B21" s="4" t="s">
+      <c r="C25" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="16"/>
+    </row>
+    <row r="26" ht="17" spans="1:4">
+      <c r="A26" s="14"/>
+      <c r="B26" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" s="10"/>
-    </row>
-    <row r="22" ht="17" spans="1:4">
-      <c r="A22" s="11"/>
-      <c r="B22" s="4" t="s">
+      <c r="C26" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" s="16"/>
+    </row>
+    <row r="27" ht="17" spans="1:4">
+      <c r="A27" s="14"/>
+      <c r="B27" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="10"/>
-    </row>
-    <row r="23" ht="17" spans="1:4">
-      <c r="A23" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D23" s="10"/>
-    </row>
-    <row r="24" ht="17" spans="1:4">
-      <c r="A24" s="11"/>
-      <c r="B24" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24" s="10"/>
-    </row>
-    <row r="25" ht="17" spans="1:4">
-      <c r="A25" s="11"/>
-      <c r="B25" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" s="10"/>
-    </row>
-    <row r="26" ht="17" spans="1:4">
-      <c r="A26" s="11"/>
-      <c r="B26" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" s="10"/>
-    </row>
-    <row r="27" ht="17" spans="1:4">
-      <c r="A27" s="11"/>
-      <c r="B27" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D27" s="10"/>
+      <c r="C27" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="16"/>
     </row>
     <row r="28" ht="17" spans="1:4">
-      <c r="A28" s="11"/>
-      <c r="B28" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D28" s="10"/>
+      <c r="A28" s="14"/>
+      <c r="B28" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3240,255 +3377,255 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="B1" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="6" t="s">
+      <c r="A4" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="11" t="s">
         <v>67</v>
       </c>
+      <c r="D4" s="11" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="5" ht="17" spans="1:4">
-      <c r="A5" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="A5" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="10"/>
+      <c r="B5" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="16"/>
     </row>
     <row r="6" ht="17" spans="1:4">
-      <c r="A6" s="11"/>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="14"/>
+      <c r="B6" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="16"/>
+    </row>
+    <row r="7" ht="17" spans="1:4">
+      <c r="A7" s="14"/>
+      <c r="B7" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="16"/>
+    </row>
+    <row r="8" ht="17" spans="1:4">
+      <c r="A8" s="14"/>
+      <c r="B8" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="16"/>
+    </row>
+    <row r="9" ht="17" spans="1:4">
+      <c r="A9" s="14"/>
+      <c r="B9" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="16"/>
+    </row>
+    <row r="10" ht="17" spans="1:4">
+      <c r="A10" s="14"/>
+      <c r="B10" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="16"/>
+    </row>
+    <row r="11" ht="17" spans="1:4">
+      <c r="A11" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="10"/>
-    </row>
-    <row r="7" ht="17" spans="1:4">
-      <c r="A7" s="11"/>
-      <c r="B7" s="4" t="s">
+      <c r="C11" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="16"/>
+    </row>
+    <row r="12" ht="17" spans="1:4">
+      <c r="A12" s="14"/>
+      <c r="B12" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="10"/>
-    </row>
-    <row r="8" ht="17" spans="1:4">
-      <c r="A8" s="11"/>
-      <c r="B8" s="4" t="s">
+      <c r="C12" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="16"/>
+    </row>
+    <row r="13" ht="17" spans="1:4">
+      <c r="A13" s="14"/>
+      <c r="B13" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="10"/>
-    </row>
-    <row r="9" ht="17" spans="1:4">
-      <c r="A9" s="11"/>
-      <c r="B9" s="4" t="s">
+      <c r="C13" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="16"/>
+    </row>
+    <row r="14" ht="17" spans="1:4">
+      <c r="A14" s="14"/>
+      <c r="B14" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="10"/>
-    </row>
-    <row r="10" ht="17" spans="1:4">
-      <c r="A10" s="11"/>
-      <c r="B10" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="10"/>
-    </row>
-    <row r="11" ht="17" spans="1:4">
-      <c r="A11" s="11" t="s">
+      <c r="C14" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="16"/>
+    </row>
+    <row r="15" ht="17" spans="1:4">
+      <c r="A15" s="14"/>
+      <c r="B15" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="10"/>
-    </row>
-    <row r="12" ht="17" spans="1:4">
-      <c r="A12" s="11"/>
-      <c r="B12" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="10"/>
-    </row>
-    <row r="13" ht="17" spans="1:4">
-      <c r="A13" s="11"/>
-      <c r="B13" s="4" t="s">
+      <c r="C15" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="16"/>
+    </row>
+    <row r="16" ht="17" spans="1:4">
+      <c r="A16" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="16"/>
+    </row>
+    <row r="17" ht="17" spans="1:4">
+      <c r="A17" s="14"/>
+      <c r="B17" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="10"/>
-    </row>
-    <row r="14" ht="17" spans="1:4">
-      <c r="A14" s="11"/>
-      <c r="B14" s="4" t="s">
+      <c r="C17" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="16"/>
+    </row>
+    <row r="18" ht="17" spans="1:4">
+      <c r="A18" s="14"/>
+      <c r="B18" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="10"/>
-    </row>
-    <row r="15" ht="17" spans="1:4">
-      <c r="A15" s="11"/>
-      <c r="B15" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="10"/>
-    </row>
-    <row r="16" ht="17" spans="1:4">
-      <c r="A16" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" s="4" t="s">
+      <c r="C18" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="16"/>
+    </row>
+    <row r="19" ht="17" spans="1:4">
+      <c r="A19" s="14"/>
+      <c r="B19" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="16"/>
+    </row>
+    <row r="20" ht="17" spans="1:4">
+      <c r="A20" s="14"/>
+      <c r="B20" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="16"/>
+    </row>
+    <row r="21" ht="17" spans="1:4">
+      <c r="A21" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="10"/>
-    </row>
-    <row r="17" ht="17" spans="1:4">
-      <c r="A17" s="11"/>
-      <c r="B17" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="10"/>
-    </row>
-    <row r="18" ht="17" spans="1:4">
-      <c r="A18" s="11"/>
-      <c r="B18" s="4" t="s">
+      <c r="B21" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="16"/>
+    </row>
+    <row r="22" ht="17" spans="1:4">
+      <c r="A22" s="14"/>
+      <c r="B22" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="10"/>
-    </row>
-    <row r="19" ht="17" spans="1:4">
-      <c r="A19" s="11"/>
-      <c r="B19" s="4" t="s">
+      <c r="C22" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="16"/>
+    </row>
+    <row r="23" ht="17" spans="1:4">
+      <c r="A23" s="14"/>
+      <c r="B23" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="10"/>
-    </row>
-    <row r="20" ht="17" spans="1:4">
-      <c r="A20" s="11"/>
-      <c r="B20" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="10"/>
-    </row>
-    <row r="21" ht="17" spans="1:4">
-      <c r="A21" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" s="10"/>
-    </row>
-    <row r="22" ht="17" spans="1:4">
-      <c r="A22" s="11"/>
-      <c r="B22" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="10"/>
-    </row>
-    <row r="23" ht="17" spans="1:4">
-      <c r="A23" s="11"/>
-      <c r="B23" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D23" s="10"/>
+      <c r="C23" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="16"/>
     </row>
     <row r="24" ht="17" spans="1:4">
-      <c r="A24" s="11"/>
-      <c r="B24" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24" s="10"/>
+      <c r="A24" s="14"/>
+      <c r="B24" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="16"/>
     </row>
     <row r="25" ht="17" spans="1:4">
-      <c r="A25" s="11"/>
-      <c r="B25" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" s="10"/>
+      <c r="A25" s="14"/>
+      <c r="B25" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3525,231 +3662,231 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="B1" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
     </row>
     <row r="2" ht="105" customHeight="1" spans="1:4">
       <c r="A2" s="2"/>
-      <c r="B2" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="4"/>
+      <c r="B2" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="9"/>
     </row>
     <row r="3" ht="21.6" customHeight="1" spans="1:4">
       <c r="A3" s="2"/>
-      <c r="B3" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="3"/>
+      <c r="B3" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="10"/>
     </row>
     <row r="4" ht="21.6" customHeight="1" spans="1:4">
       <c r="A4" s="2"/>
-      <c r="B4" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="3"/>
+      <c r="B4" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="10"/>
     </row>
     <row r="5" ht="17.15" customHeight="1" spans="1:4">
       <c r="A5" s="2"/>
-      <c r="B5" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="4"/>
+      <c r="B5" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="9"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="6" t="s">
+      <c r="A6" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="B6" s="12"/>
+      <c r="C6" s="11" t="s">
         <v>67</v>
       </c>
+      <c r="D6" s="11" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="7" ht="17" spans="1:4">
-      <c r="A7" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="10"/>
+      <c r="A7" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="16"/>
     </row>
     <row r="8" ht="17" spans="1:4">
-      <c r="A8" s="11"/>
-      <c r="B8" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="10"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="16"/>
     </row>
     <row r="9" ht="17" spans="1:4">
-      <c r="A9" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="10"/>
+      <c r="A9" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="16"/>
     </row>
     <row r="10" ht="17" spans="1:4">
-      <c r="A10" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="10"/>
+      <c r="A10" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="16"/>
     </row>
     <row r="11" ht="17" spans="1:4">
-      <c r="A11" s="11"/>
-      <c r="B11" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="10"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="16"/>
     </row>
     <row r="12" ht="17" spans="1:4">
-      <c r="A12" s="11"/>
-      <c r="B12" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="10"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="16"/>
     </row>
     <row r="13" ht="84" spans="1:4">
-      <c r="A13" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>89</v>
+      <c r="A13" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="14" ht="84" spans="1:4">
-      <c r="A14" s="11"/>
-      <c r="B14" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>90</v>
+      <c r="A14" s="14"/>
+      <c r="B14" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="15" ht="84" spans="1:4">
-      <c r="A15" s="11"/>
-      <c r="B15" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>91</v>
+      <c r="A15" s="14"/>
+      <c r="B15" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="16" ht="17" spans="1:4">
-      <c r="A16" s="11"/>
-      <c r="B16" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="10"/>
+      <c r="A16" s="14"/>
+      <c r="B16" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="16"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="11"/>
-      <c r="B17" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="10"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="16"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B18" s="16" t="s">
+      <c r="A18" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="13"/>
+      <c r="B18" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="20"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="11"/>
-      <c r="B19" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="13"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="20"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="11"/>
-      <c r="B20" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="13"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="20"/>
     </row>
     <row r="21" ht="17" spans="1:4">
-      <c r="A21" s="11"/>
-      <c r="B21" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="13"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3789,249 +3926,249 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="B1" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
     </row>
     <row r="2" ht="18.65" customHeight="1" spans="1:4">
       <c r="A2" s="2"/>
-      <c r="B2" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="4"/>
+      <c r="B2" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="9"/>
     </row>
     <row r="3" ht="21.6" customHeight="1" spans="1:4">
       <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="3"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="10"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="6" t="s">
+      <c r="A4" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="11" t="s">
         <v>67</v>
       </c>
+      <c r="D4" s="11" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="5" ht="17" spans="1:4">
-      <c r="A5" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="10" t="s">
+      <c r="A5" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>101</v>
       </c>
+      <c r="C5" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="6" ht="17" spans="1:4">
-      <c r="A6" s="11"/>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="14"/>
+      <c r="B6" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="10" t="s">
+    </row>
+    <row r="7" ht="17" spans="1:4">
+      <c r="A7" s="14"/>
+      <c r="B7" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" ht="17" spans="1:4">
+      <c r="A8" s="14"/>
+      <c r="B8" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" ht="17" spans="1:4">
+      <c r="A9" s="14"/>
+      <c r="B9" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" ht="17" spans="1:4">
+      <c r="A10" s="14"/>
+      <c r="B10" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="16"/>
+    </row>
+    <row r="11" ht="17" spans="1:4">
+      <c r="A11" s="14"/>
+      <c r="B11" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="16"/>
+    </row>
+    <row r="12" ht="17" spans="1:4">
+      <c r="A12" s="14"/>
+      <c r="B12" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="16"/>
+    </row>
+    <row r="13" ht="17" spans="1:4">
+      <c r="A13" s="14"/>
+      <c r="B13" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="16"/>
+    </row>
+    <row r="14" ht="17" spans="1:4">
+      <c r="A14" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="7" ht="17" spans="1:4">
-      <c r="A7" s="11"/>
-      <c r="B7" s="4" t="s">
+      <c r="C14" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="9"/>
+    </row>
+    <row r="15" ht="17" spans="1:4">
+      <c r="A15" s="14"/>
+      <c r="B15" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" ht="17" spans="1:4">
-      <c r="A8" s="11"/>
-      <c r="B8" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="9" ht="17" spans="1:4">
-      <c r="A9" s="11"/>
-      <c r="B9" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" ht="17" spans="1:4">
-      <c r="A10" s="11"/>
-      <c r="B10" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="10"/>
-    </row>
-    <row r="11" ht="17" spans="1:4">
-      <c r="A11" s="11"/>
-      <c r="B11" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="10"/>
-    </row>
-    <row r="12" ht="17" spans="1:4">
-      <c r="A12" s="11"/>
-      <c r="B12" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="10"/>
-    </row>
-    <row r="13" ht="17" spans="1:4">
-      <c r="A13" s="11"/>
-      <c r="B13" s="4" t="s">
+      <c r="C15" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="9"/>
+    </row>
+    <row r="16" ht="17" spans="1:4">
+      <c r="A16" s="14"/>
+      <c r="B16" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="9"/>
+    </row>
+    <row r="17" ht="18" spans="1:4">
+      <c r="A17" s="14"/>
+      <c r="B17" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" ht="18" spans="1:4">
+      <c r="A18" s="14"/>
+      <c r="B18" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="16"/>
+    </row>
+    <row r="19" ht="18" spans="1:4">
+      <c r="A19" s="14"/>
+      <c r="B19" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="20"/>
+    </row>
+    <row r="20" ht="18" spans="1:4">
+      <c r="A20" s="14"/>
+      <c r="B20" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="20"/>
+    </row>
+    <row r="21" ht="18" spans="1:4">
+      <c r="A21" s="14"/>
+      <c r="B21" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="20"/>
+    </row>
+    <row r="22" ht="17" spans="1:4">
+      <c r="A22" s="14"/>
+      <c r="B22" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="10"/>
-    </row>
-    <row r="14" ht="17" spans="1:4">
-      <c r="A14" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15" ht="17" spans="1:4">
-      <c r="A15" s="11"/>
-      <c r="B15" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16" ht="17" spans="1:4">
-      <c r="A16" s="11"/>
-      <c r="B16" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17" ht="18" spans="1:4">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" ht="18" spans="1:4">
-      <c r="A18" s="11"/>
-      <c r="B18" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="10"/>
-    </row>
-    <row r="19" ht="18" spans="1:4">
-      <c r="A19" s="11"/>
-      <c r="B19" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="13"/>
-    </row>
-    <row r="20" ht="18" spans="1:4">
-      <c r="A20" s="11"/>
-      <c r="B20" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="13"/>
-    </row>
-    <row r="21" ht="18" spans="1:4">
-      <c r="A21" s="11"/>
-      <c r="B21" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" s="13"/>
-    </row>
-    <row r="22" ht="17" spans="1:4">
-      <c r="A22" s="11"/>
-      <c r="B22" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="13"/>
+      <c r="C22" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="20"/>
     </row>
     <row r="23" ht="17" spans="1:4">
-      <c r="A23" s="11"/>
-      <c r="B23" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="13"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4054,340 +4191,1050 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="3"/>
+  <dimension ref="A1:E39"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="64.0961538461538" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.9038461538462" style="1" customWidth="1"/>
-    <col min="4" max="4" width="47.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="64.0961538461538" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.9038461538462" style="1" customWidth="1"/>
+    <col min="5" max="5" width="47.75" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:4">
+    <row r="1" customHeight="1" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-    </row>
-    <row r="2" ht="18.65" customHeight="1" spans="1:4">
+      <c r="B1" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+    </row>
+    <row r="2" ht="18.65" customHeight="1" spans="1:5">
       <c r="A2" s="2"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="4"/>
-    </row>
-    <row r="3" ht="21.6" customHeight="1" spans="1:4">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="9"/>
+    </row>
+    <row r="3" ht="21.6" customHeight="1" spans="1:5">
       <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" ht="21.6" customHeight="1" spans="1:4">
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" ht="21.6" customHeight="1" spans="1:5">
       <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="6" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="10"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="B5" s="11"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="11" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="6" ht="17" spans="1:4">
-      <c r="A6" s="8" t="s">
+      <c r="E5" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="4" t="s">
+    </row>
+    <row r="6" ht="17" spans="1:5">
+      <c r="A6" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="16"/>
+    </row>
+    <row r="7" ht="17" spans="1:5">
+      <c r="A7" s="14"/>
+      <c r="B7" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="16"/>
+    </row>
+    <row r="8" ht="17" spans="1:5">
+      <c r="A8" s="14"/>
+      <c r="B8" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="16"/>
+    </row>
+    <row r="9" ht="17" spans="1:5">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="16"/>
+    </row>
+    <row r="10" ht="17" spans="1:5">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="16"/>
+    </row>
+    <row r="11" ht="17" spans="1:5">
+      <c r="A11" s="14"/>
+      <c r="B11" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="16"/>
+    </row>
+    <row r="12" ht="17" spans="1:5">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="16"/>
+    </row>
+    <row r="13" ht="17" spans="1:5">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="16"/>
+    </row>
+    <row r="14" ht="17" spans="1:5">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="16"/>
+    </row>
+    <row r="15" ht="17" spans="1:5">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="16"/>
+    </row>
+    <row r="16" ht="17" spans="1:5">
+      <c r="A16" s="14"/>
+      <c r="B16" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="10"/>
-    </row>
-    <row r="7" ht="17" spans="1:4">
-      <c r="A7" s="8"/>
-      <c r="B7" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="10"/>
-    </row>
-    <row r="8" ht="17" spans="1:4">
-      <c r="A8" s="8"/>
-      <c r="B8" s="4" t="s">
+      <c r="D16" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="16"/>
+    </row>
+    <row r="17" ht="17" spans="1:5">
+      <c r="A17" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="10"/>
-    </row>
-    <row r="9" ht="17" spans="1:4">
-      <c r="A9" s="8"/>
-      <c r="B9" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="10"/>
-    </row>
-    <row r="10" ht="17" spans="1:4">
-      <c r="A10" s="8"/>
-      <c r="B10" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="10"/>
-    </row>
-    <row r="11" ht="17" spans="1:4">
-      <c r="A11" s="8"/>
-      <c r="B11" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="10"/>
-    </row>
-    <row r="12" ht="17" spans="1:4">
-      <c r="A12" s="8"/>
-      <c r="B12" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="10"/>
-    </row>
-    <row r="13" ht="17" spans="1:4">
-      <c r="A13" s="8"/>
-      <c r="B13" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="10"/>
-    </row>
-    <row r="14" ht="17" spans="1:4">
-      <c r="A14" s="8"/>
-      <c r="B14" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="10"/>
-    </row>
-    <row r="15" ht="17" spans="1:4">
-      <c r="A15" s="8"/>
-      <c r="B15" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="10"/>
-    </row>
-    <row r="16" ht="17" spans="1:4">
-      <c r="A16" s="8"/>
-      <c r="B16" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="10"/>
-    </row>
-    <row r="17" ht="17" spans="1:4">
-      <c r="A17" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>126</v>
-      </c>
       <c r="C17" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="18" ht="34" spans="1:4">
-      <c r="A18" s="11"/>
-      <c r="B18" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="4" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="19" ht="17" spans="1:4">
-      <c r="A19" s="11"/>
-      <c r="B19" s="4" t="s">
+      <c r="D17" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" ht="34" spans="1:5">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="19" ht="17" spans="1:5">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="20" ht="17" spans="1:4">
-      <c r="A20" s="11"/>
-      <c r="B20" s="4" t="s">
+      <c r="D19" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" ht="17" spans="1:5">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="11"/>
-      <c r="C21" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="10"/>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="11"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="10"/>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="10"/>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="11"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" s="4"/>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="11"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="4"/>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="11"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27" ht="17.6" spans="1:4">
-      <c r="A27" s="11"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" s="12"/>
-    </row>
-    <row r="28" ht="17.6" spans="1:4">
-      <c r="A28" s="11"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" s="10"/>
-    </row>
-    <row r="29" ht="17.6" spans="1:4">
-      <c r="A29" s="11" t="s">
+      <c r="D20" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="14"/>
+      <c r="B21" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="16"/>
+    </row>
+    <row r="22" ht="17" spans="1:5">
+      <c r="A22" s="14"/>
+      <c r="B22" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="16"/>
+    </row>
+    <row r="23" ht="17" spans="1:5">
+      <c r="A23" s="14"/>
+      <c r="B23" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="16"/>
+    </row>
+    <row r="24" ht="17" spans="1:5">
+      <c r="A24" s="14"/>
+      <c r="B24" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="16"/>
+    </row>
+    <row r="25" ht="17" spans="1:5">
+      <c r="A25" s="14"/>
+      <c r="B25" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="16"/>
+    </row>
+    <row r="26" ht="17" spans="1:5">
+      <c r="A26" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" s="13"/>
-    </row>
-    <row r="30" ht="17.6" spans="1:4">
-      <c r="A30" s="11"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D30" s="13"/>
-    </row>
-    <row r="31" ht="17.6" spans="1:4">
-      <c r="A31" s="11"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31" s="13"/>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="11"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D32" s="13"/>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="11"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D33" s="13"/>
+      <c r="B26" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="16"/>
+    </row>
+    <row r="27" ht="17" spans="1:5">
+      <c r="A27" s="14"/>
+      <c r="B27" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="9"/>
+    </row>
+    <row r="28" ht="17" spans="1:5">
+      <c r="A28" s="14"/>
+      <c r="B28" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="9"/>
+    </row>
+    <row r="29" ht="17" spans="1:5">
+      <c r="A29" s="14"/>
+      <c r="B29" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="9"/>
+    </row>
+    <row r="30" ht="17" spans="1:5">
+      <c r="A30" s="14"/>
+      <c r="B30" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="9"/>
+    </row>
+    <row r="31" ht="17.6" spans="1:5">
+      <c r="A31" s="14"/>
+      <c r="B31" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="19"/>
+    </row>
+    <row r="32" ht="17" spans="1:5">
+      <c r="A32" s="14"/>
+      <c r="B32" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" s="16"/>
+    </row>
+    <row r="33" ht="17" spans="1:5">
+      <c r="A33" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" s="20"/>
+    </row>
+    <row r="34" ht="17" spans="1:5">
+      <c r="A34" s="14"/>
+      <c r="B34" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="20"/>
+    </row>
+    <row r="35" ht="17" spans="1:5">
+      <c r="A35" s="14"/>
+      <c r="B35" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="20"/>
+    </row>
+    <row r="36" ht="17" spans="1:5">
+      <c r="A36" s="14"/>
+      <c r="B36" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="20"/>
+    </row>
+    <row r="37" ht="17" spans="1:5">
+      <c r="A37" s="14"/>
+      <c r="B37" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" s="20"/>
+    </row>
+    <row r="38" ht="17" spans="1:5">
+      <c r="A38" s="14"/>
+      <c r="B38" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" s="20"/>
+    </row>
+    <row r="39" ht="17" spans="1:5">
+      <c r="A39" s="14"/>
+      <c r="B39" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E39" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B1:D1"/>
+  <mergeCells count="9">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
     <mergeCell ref="A1:A4"/>
     <mergeCell ref="A6:A16"/>
-    <mergeCell ref="A17:A22"/>
-    <mergeCell ref="A23:A28"/>
-    <mergeCell ref="A29:A33"/>
+    <mergeCell ref="A17:A25"/>
+    <mergeCell ref="A26:A32"/>
+    <mergeCell ref="A33:A39"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C19 C20 C2:C4 C6:C18 C21:C33">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D18 D39 D2:D4 D6:D17 D19:D21 D22:D38">
+      <formula1>"未进行,进行中,已暂停,已完成"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <cols>
+    <col min="3" max="3" width="64.0961538461538" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.9038461538462" style="1" customWidth="1"/>
+    <col min="5" max="5" width="47.75" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customHeight="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="5"/>
+    </row>
+    <row r="2" ht="18.65" customHeight="1" spans="1:5">
+      <c r="A2" s="2"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="9"/>
+    </row>
+    <row r="3" ht="21.6" customHeight="1" spans="1:5">
+      <c r="A3" s="2"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" ht="21.6" customHeight="1" spans="1:5">
+      <c r="A4" s="2"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="10"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" ht="17" spans="1:5">
+      <c r="A6" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="16"/>
+    </row>
+    <row r="7" ht="17" spans="1:5">
+      <c r="A7" s="17"/>
+      <c r="B7" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="16"/>
+    </row>
+    <row r="8" ht="17" spans="1:5">
+      <c r="A8" s="17"/>
+      <c r="B8" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="16"/>
+    </row>
+    <row r="9" ht="17" spans="1:5">
+      <c r="A9" s="17"/>
+      <c r="B9" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="16"/>
+    </row>
+    <row r="10" ht="17" spans="1:5">
+      <c r="A10" s="17"/>
+      <c r="B10" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="16"/>
+    </row>
+    <row r="11" ht="17" spans="1:5">
+      <c r="A11" s="17"/>
+      <c r="B11" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="16"/>
+    </row>
+    <row r="12" ht="17" spans="1:5">
+      <c r="A12" s="17"/>
+      <c r="B12" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="16"/>
+    </row>
+    <row r="13" ht="17" spans="1:5">
+      <c r="A13" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="16"/>
+    </row>
+    <row r="14" ht="17" spans="1:5">
+      <c r="A14" s="17"/>
+      <c r="B14" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="16"/>
+    </row>
+    <row r="15" ht="17" spans="1:5">
+      <c r="A15" s="17"/>
+      <c r="B15" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="16"/>
+    </row>
+    <row r="16" ht="17" spans="1:5">
+      <c r="A16" s="17"/>
+      <c r="B16" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="16"/>
+    </row>
+    <row r="17" ht="17" spans="1:5">
+      <c r="A17" s="17"/>
+      <c r="B17" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="9"/>
+    </row>
+    <row r="18" ht="17" spans="1:5">
+      <c r="A18" s="17"/>
+      <c r="B18" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="16"/>
+    </row>
+    <row r="19" ht="17" spans="1:5">
+      <c r="A19" s="17"/>
+      <c r="B19" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="16"/>
+    </row>
+    <row r="20" ht="17" spans="1:5">
+      <c r="A20" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="16"/>
+    </row>
+    <row r="21" ht="17" spans="1:5">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="9"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="14"/>
+      <c r="B22" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="9"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="14"/>
+      <c r="B23" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="9"/>
+      <c r="D23" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="9"/>
+    </row>
+    <row r="24" ht="17.6" spans="1:5">
+      <c r="A24" s="14"/>
+      <c r="B24" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="19"/>
+    </row>
+    <row r="25" ht="17.6" spans="1:5">
+      <c r="A25" s="14"/>
+      <c r="B25" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="16"/>
+    </row>
+    <row r="26" ht="17.6" spans="1:5">
+      <c r="A26" s="14"/>
+      <c r="B26" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="16"/>
+    </row>
+    <row r="27" ht="17.6" spans="1:5">
+      <c r="A27" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="20"/>
+    </row>
+    <row r="28" ht="17.6" spans="1:5">
+      <c r="A28" s="14"/>
+      <c r="B28" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="20"/>
+    </row>
+    <row r="29" ht="17.6" spans="1:5">
+      <c r="A29" s="14"/>
+      <c r="B29" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="D29" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="20"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="14"/>
+      <c r="B30" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" s="9"/>
+      <c r="D30" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="20"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="14"/>
+      <c r="B31" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="20"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="14"/>
+      <c r="B32" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C32" s="9"/>
+      <c r="D32" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" s="20"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="14"/>
+      <c r="B33" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C33" s="9"/>
+      <c r="D33" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" s="20"/>
+    </row>
+    <row r="34" ht="17.6" spans="1:5">
+      <c r="A34" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C34" s="19"/>
+      <c r="D34" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="20"/>
+    </row>
+    <row r="35" ht="17.6" spans="1:5">
+      <c r="A35" s="14"/>
+      <c r="B35" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="C35" s="19"/>
+      <c r="D35" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="20"/>
+    </row>
+    <row r="36" ht="17.6" spans="1:5">
+      <c r="A36" s="14"/>
+      <c r="B36" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C36" s="19"/>
+      <c r="D36" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="20"/>
+    </row>
+    <row r="37" ht="17.6" spans="1:5">
+      <c r="A37" s="14"/>
+      <c r="B37" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C37" s="19"/>
+      <c r="D37" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" s="20"/>
+    </row>
+    <row r="38" ht="17.6" spans="1:5">
+      <c r="A38" s="14"/>
+      <c r="B38" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C38" s="19"/>
+      <c r="D38" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" s="20"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="14"/>
+      <c r="B39" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C39" s="9"/>
+      <c r="D39" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E39" s="20"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="14"/>
+      <c r="B40" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C40" s="9"/>
+      <c r="D40" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E40" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="A6:A12"/>
+    <mergeCell ref="A13:A19"/>
+    <mergeCell ref="A20:A26"/>
+    <mergeCell ref="A27:A33"/>
+    <mergeCell ref="A34:A40"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D25 D2:D4 D6:D12 D13:D19 D20:D24 D26:D28 D29:D37 D38:D40">
       <formula1>"未进行,进行中,已暂停,已完成"</formula1>
     </dataValidation>
   </dataValidations>
